--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127778500</v>
+        <v>127774666</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628416</v>
+        <v>628697</v>
       </c>
       <c r="R2" t="n">
-        <v>6918738</v>
+        <v>6918580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -873,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127774666</v>
+        <v>127775382</v>
       </c>
       <c r="B4" t="n">
-        <v>91332</v>
+        <v>98484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628697</v>
+        <v>628614</v>
       </c>
       <c r="R4" t="n">
-        <v>6918580</v>
+        <v>6918662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,45 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775382</v>
+        <v>127778500</v>
       </c>
       <c r="B5" t="n">
-        <v>98484</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628614</v>
+        <v>628416</v>
       </c>
       <c r="R5" t="n">
-        <v>6918662</v>
+        <v>6918738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1265,45 +1265,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127774181</v>
+        <v>127778802</v>
       </c>
       <c r="B8" t="n">
-        <v>91297</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628716</v>
+        <v>628634</v>
       </c>
       <c r="R8" t="n">
-        <v>6918568</v>
+        <v>6918656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,49 +1366,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127778802</v>
+        <v>127774181</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>91297</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628634</v>
+        <v>628716</v>
       </c>
       <c r="R9" t="n">
-        <v>6918656</v>
+        <v>6918568</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127774280</v>
+        <v>127775315</v>
       </c>
       <c r="B10" t="n">
         <v>98450</v>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628702</v>
+        <v>628627</v>
       </c>
       <c r="R10" t="n">
-        <v>6918572</v>
+        <v>6918612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,49 +1564,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127777577</v>
+        <v>127778586</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628305</v>
+        <v>628451</v>
       </c>
       <c r="R11" t="n">
-        <v>6918693</v>
+        <v>6918725</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,45 +1661,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127778586</v>
+        <v>127775915</v>
       </c>
       <c r="B12" t="n">
-        <v>98367</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628451</v>
+        <v>628612</v>
       </c>
       <c r="R12" t="n">
-        <v>6918725</v>
+        <v>6918686</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127775915</v>
+        <v>127774280</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628612</v>
+        <v>628702</v>
       </c>
       <c r="R13" t="n">
-        <v>6918686</v>
+        <v>6918572</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127775315</v>
+        <v>127777577</v>
       </c>
       <c r="B14" t="n">
         <v>98450</v>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628627</v>
+        <v>628305</v>
       </c>
       <c r="R14" t="n">
-        <v>6918612</v>
+        <v>6918693</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,38 +1964,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777999</v>
+        <v>127776730</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>92621</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1435</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2004,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628284</v>
+        <v>628590</v>
       </c>
       <c r="R15" t="n">
-        <v>6918798</v>
+        <v>6918692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,11 +2044,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,42 +2171,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127776730</v>
+        <v>127777999</v>
       </c>
       <c r="B17" t="n">
-        <v>92621</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1435</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2216,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628590</v>
+        <v>628284</v>
       </c>
       <c r="R17" t="n">
-        <v>6918692</v>
+        <v>6918798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,6 +2247,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2278,49 +2278,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127774703</v>
+        <v>127775800</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628693</v>
+        <v>628598</v>
       </c>
       <c r="R18" t="n">
-        <v>6918589</v>
+        <v>6918637</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,45 +2375,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127775800</v>
+        <v>127774703</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628598</v>
+        <v>628693</v>
       </c>
       <c r="R19" t="n">
-        <v>6918637</v>
+        <v>6918589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,37 +2577,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127777244</v>
+        <v>127775985</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>28</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2616,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628416</v>
+        <v>628607</v>
       </c>
       <c r="R21" t="n">
-        <v>6918688</v>
+        <v>6918700</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,38 +2679,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127775985</v>
+        <v>127777244</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628607</v>
+        <v>628416</v>
       </c>
       <c r="R22" t="n">
-        <v>6918700</v>
+        <v>6918688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,37 +2881,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127776177</v>
+        <v>127777664</v>
       </c>
       <c r="B24" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2920,10 +2921,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628595</v>
+        <v>628294</v>
       </c>
       <c r="R24" t="n">
-        <v>6918652</v>
+        <v>6918677</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2960,7 +2961,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Förekommer inom våt området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2987,45 +2988,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776370</v>
+        <v>127775258</v>
       </c>
       <c r="B25" t="n">
-        <v>98484</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628595</v>
+        <v>628620</v>
       </c>
       <c r="R25" t="n">
-        <v>6918652</v>
+        <v>6918640</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,49 +3089,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127775258</v>
+        <v>127776370</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>98484</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628620</v>
+        <v>628595</v>
       </c>
       <c r="R26" t="n">
-        <v>6918640</v>
+        <v>6918652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,38 +3186,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127777664</v>
+        <v>127776177</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>98367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628294</v>
+        <v>628595</v>
       </c>
       <c r="R27" t="n">
-        <v>6918677</v>
+        <v>6918652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3696,7 +3696,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127778213</v>
+        <v>127777928</v>
       </c>
       <c r="B32" t="n">
         <v>98450</v>
@@ -3726,12 +3726,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628284</v>
+        <v>628289</v>
       </c>
       <c r="R32" t="n">
-        <v>6918798</v>
+        <v>6918777</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3802,7 +3797,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127777928</v>
+        <v>127778213</v>
       </c>
       <c r="B33" t="n">
         <v>98450</v>
@@ -3832,7 +3827,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628289</v>
+        <v>628284</v>
       </c>
       <c r="R33" t="n">
-        <v>6918777</v>
+        <v>6918798</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4503,45 +4503,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127777102</v>
+        <v>127774434</v>
       </c>
       <c r="B40" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628441</v>
+        <v>628697</v>
       </c>
       <c r="R40" t="n">
-        <v>6918705</v>
+        <v>6918580</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4701,49 +4705,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127774434</v>
+        <v>127774928</v>
       </c>
       <c r="B42" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628697</v>
+        <v>628665</v>
       </c>
       <c r="R42" t="n">
-        <v>6918580</v>
+        <v>6918587</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127774928</v>
+        <v>127777102</v>
       </c>
       <c r="B43" t="n">
         <v>91332</v>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628665</v>
+        <v>628441</v>
       </c>
       <c r="R43" t="n">
-        <v>6918587</v>
+        <v>6918705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4996,37 +4996,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127776693</v>
+        <v>127778954</v>
       </c>
       <c r="B45" t="n">
-        <v>98450</v>
+        <v>92622</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5035,10 +5040,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628590</v>
+        <v>628675</v>
       </c>
       <c r="R45" t="n">
-        <v>6918692</v>
+        <v>6918656</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5097,37 +5102,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127775358</v>
+        <v>127774067</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5136,10 +5142,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628614</v>
+        <v>628716</v>
       </c>
       <c r="R46" t="n">
-        <v>6918662</v>
+        <v>6918568</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5198,7 +5204,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127775875</v>
+        <v>127777752</v>
       </c>
       <c r="B47" t="n">
         <v>98450</v>
@@ -5228,7 +5234,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5237,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628595</v>
+        <v>628353</v>
       </c>
       <c r="R47" t="n">
-        <v>6918652</v>
+        <v>6918711</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5273,11 +5279,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5304,7 +5305,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127777752</v>
+        <v>127776693</v>
       </c>
       <c r="B48" t="n">
         <v>98450</v>
@@ -5334,7 +5335,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5343,10 +5344,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628353</v>
+        <v>628590</v>
       </c>
       <c r="R48" t="n">
-        <v>6918711</v>
+        <v>6918692</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5405,42 +5406,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127778954</v>
+        <v>127775875</v>
       </c>
       <c r="B49" t="n">
-        <v>92622</v>
+        <v>98450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5449,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628675</v>
+        <v>628595</v>
       </c>
       <c r="R49" t="n">
-        <v>6918656</v>
+        <v>6918652</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5485,6 +5481,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5511,38 +5512,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127774067</v>
+        <v>127775358</v>
       </c>
       <c r="B50" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628716</v>
+        <v>628614</v>
       </c>
       <c r="R50" t="n">
-        <v>6918568</v>
+        <v>6918662</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127774666</v>
       </c>
       <c r="B2" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127778961</v>
       </c>
       <c r="B3" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127775382</v>
+        <v>127778500</v>
       </c>
       <c r="B4" t="n">
-        <v>98484</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628614</v>
+        <v>628416</v>
       </c>
       <c r="R4" t="n">
-        <v>6918662</v>
+        <v>6918738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127778500</v>
+        <v>127775156</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,7 +1000,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1005,13 +1009,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628416</v>
+        <v>628642</v>
       </c>
       <c r="R5" t="n">
-        <v>6918738</v>
+        <v>6918602</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,52 +1071,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775156</v>
+        <v>127775382</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628642</v>
+        <v>628614</v>
       </c>
       <c r="R6" t="n">
-        <v>6918602</v>
+        <v>6918662</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127775456</v>
       </c>
       <c r="B7" t="n">
-        <v>98484</v>
+        <v>98490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,49 +1265,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778802</v>
+        <v>127774181</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>91303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628634</v>
+        <v>628716</v>
       </c>
       <c r="R8" t="n">
-        <v>6918656</v>
+        <v>6918568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,45 +1362,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774181</v>
+        <v>127778802</v>
       </c>
       <c r="B9" t="n">
-        <v>91297</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628716</v>
+        <v>628634</v>
       </c>
       <c r="R9" t="n">
-        <v>6918568</v>
+        <v>6918656</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127775315</v>
+        <v>127774280</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628627</v>
+        <v>628702</v>
       </c>
       <c r="R10" t="n">
-        <v>6918612</v>
+        <v>6918572</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,7 +1567,7 @@
         <v>127778586</v>
       </c>
       <c r="B11" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>127775915</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127774280</v>
+        <v>127777577</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628702</v>
+        <v>628305</v>
       </c>
       <c r="R13" t="n">
-        <v>6918572</v>
+        <v>6918693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127777577</v>
+        <v>127775315</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628305</v>
+        <v>628627</v>
       </c>
       <c r="R14" t="n">
-        <v>6918693</v>
+        <v>6918612</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,42 +1964,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127776730</v>
+        <v>127777999</v>
       </c>
       <c r="B15" t="n">
-        <v>92621</v>
+        <v>57660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1435</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2008,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628590</v>
+        <v>628284</v>
       </c>
       <c r="R15" t="n">
-        <v>6918692</v>
+        <v>6918798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,6 +2040,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2070,37 +2071,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127778755</v>
+        <v>127776730</v>
       </c>
       <c r="B16" t="n">
-        <v>98484</v>
+        <v>92627</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>1435</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2109,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628626</v>
+        <v>628590</v>
       </c>
       <c r="R16" t="n">
-        <v>6918669</v>
+        <v>6918692</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2171,38 +2177,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127777999</v>
+        <v>127778755</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>98490</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2211,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628284</v>
+        <v>628626</v>
       </c>
       <c r="R17" t="n">
-        <v>6918798</v>
+        <v>6918669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,11 +2252,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2281,7 +2281,7 @@
         <v>127775800</v>
       </c>
       <c r="B18" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127774703</v>
+        <v>127777111</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>65</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628693</v>
+        <v>628453</v>
       </c>
       <c r="R19" t="n">
-        <v>6918589</v>
+        <v>6918694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777111</v>
+        <v>127774703</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628453</v>
+        <v>628693</v>
       </c>
       <c r="R20" t="n">
-        <v>6918694</v>
+        <v>6918589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,7 +2682,7 @@
         <v>127777244</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>127778761</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127775258</v>
+        <v>127775318</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3089,10 +3089,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127776370</v>
+        <v>127776177</v>
       </c>
       <c r="B26" t="n">
-        <v>98484</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,24 +3100,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3160,6 +3164,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3186,10 +3195,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127776177</v>
+        <v>127776370</v>
       </c>
       <c r="B27" t="n">
-        <v>98367</v>
+        <v>98490</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,28 +3206,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3261,11 +3266,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127774870</v>
+        <v>127776178</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628653</v>
+        <v>628598</v>
       </c>
       <c r="R28" t="n">
-        <v>6918622</v>
+        <v>6918670</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127776178</v>
+        <v>127777628</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628598</v>
+        <v>628304</v>
       </c>
       <c r="R29" t="n">
-        <v>6918670</v>
+        <v>6918675</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127777628</v>
+        <v>127774870</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628304</v>
+        <v>628653</v>
       </c>
       <c r="R30" t="n">
-        <v>6918675</v>
+        <v>6918622</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
         <v>127776816</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127777928</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127778213</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127775104</v>
       </c>
       <c r="B34" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127778222</v>
       </c>
       <c r="B35" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127778286</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>127776189</v>
       </c>
       <c r="B38" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>127777903</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,49 +4503,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127774434</v>
+        <v>127778769</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>91338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628697</v>
+        <v>628626</v>
       </c>
       <c r="R40" t="n">
-        <v>6918580</v>
+        <v>6918669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4604,49 +4600,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127777316</v>
+        <v>127774928</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>91338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628396</v>
+        <v>628665</v>
       </c>
       <c r="R41" t="n">
-        <v>6918706</v>
+        <v>6918587</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4705,10 +4697,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127774928</v>
+        <v>127777102</v>
       </c>
       <c r="B42" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628665</v>
+        <v>628441</v>
       </c>
       <c r="R42" t="n">
-        <v>6918587</v>
+        <v>6918705</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4802,45 +4794,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127777102</v>
+        <v>127774434</v>
       </c>
       <c r="B43" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628441</v>
+        <v>628697</v>
       </c>
       <c r="R43" t="n">
-        <v>6918705</v>
+        <v>6918580</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4899,45 +4895,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127778769</v>
+        <v>127777316</v>
       </c>
       <c r="B44" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628626</v>
+        <v>628396</v>
       </c>
       <c r="R44" t="n">
-        <v>6918669</v>
+        <v>6918706</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,42 +4996,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127778954</v>
+        <v>127776693</v>
       </c>
       <c r="B45" t="n">
-        <v>92622</v>
+        <v>98456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5040,10 +5035,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628675</v>
+        <v>628590</v>
       </c>
       <c r="R45" t="n">
-        <v>6918656</v>
+        <v>6918692</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5102,38 +5097,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127774067</v>
+        <v>127774205</v>
       </c>
       <c r="B46" t="n">
-        <v>57823</v>
+        <v>98456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5142,10 +5136,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628716</v>
+        <v>628710</v>
       </c>
       <c r="R46" t="n">
-        <v>6918568</v>
+        <v>6918574</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5178,6 +5172,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5204,37 +5203,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127777752</v>
+        <v>127778954</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>92628</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5243,10 +5247,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628353</v>
+        <v>628675</v>
       </c>
       <c r="R47" t="n">
-        <v>6918711</v>
+        <v>6918656</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5305,37 +5309,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127776693</v>
+        <v>127774067</v>
       </c>
       <c r="B48" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5344,10 +5349,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628590</v>
+        <v>628716</v>
       </c>
       <c r="R48" t="n">
-        <v>6918692</v>
+        <v>6918568</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5406,10 +5411,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127775875</v>
+        <v>127775358</v>
       </c>
       <c r="B49" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5436,7 +5441,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5445,10 +5450,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628595</v>
+        <v>628614</v>
       </c>
       <c r="R49" t="n">
-        <v>6918652</v>
+        <v>6918662</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,11 +5486,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5512,10 +5512,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127775358</v>
+        <v>127777752</v>
       </c>
       <c r="B50" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628614</v>
+        <v>628353</v>
       </c>
       <c r="R50" t="n">
-        <v>6918662</v>
+        <v>6918711</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127774205</v>
+        <v>127775875</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5652,10 +5652,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628710</v>
+        <v>628595</v>
       </c>
       <c r="R51" t="n">
-        <v>6918574</v>
+        <v>6918652</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Påväg att blomma</t>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5722,7 +5722,7 @@
         <v>127774353</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5817,6 +5817,495 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127834723</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Djupmyran, Djupmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>628436</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6918767</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127836030</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Djupmyran, Djupmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>628578</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6918653</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127836087</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Djupmyran, Djupmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>628569</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6918667</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127833952</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Djupmyran, Djupmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>628647</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6918692</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127834972</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98490</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Djupmyran, Djupmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>628267</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6918732</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anna Nordbäck</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127774666</v>
+        <v>127778500</v>
       </c>
       <c r="B2" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628697</v>
+        <v>628416</v>
       </c>
       <c r="R2" t="n">
-        <v>6918580</v>
+        <v>6918738</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,48 +776,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127778961</v>
+        <v>127775156</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628684</v>
+        <v>628642</v>
       </c>
       <c r="R3" t="n">
-        <v>6918685</v>
+        <v>6918602</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,49 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778500</v>
+        <v>127778961</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>97336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628416</v>
+        <v>628684</v>
       </c>
       <c r="R4" t="n">
-        <v>6918738</v>
+        <v>6918685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,52 +974,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775156</v>
+        <v>127775382</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628642</v>
+        <v>628614</v>
       </c>
       <c r="R5" t="n">
-        <v>6918602</v>
+        <v>6918662</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775382</v>
+        <v>127774666</v>
       </c>
       <c r="B6" t="n">
-        <v>98490</v>
+        <v>91341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628614</v>
+        <v>628697</v>
       </c>
       <c r="R6" t="n">
-        <v>6918662</v>
+        <v>6918580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
         <v>127775456</v>
       </c>
       <c r="B7" t="n">
-        <v>98490</v>
+        <v>98493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127774181</v>
       </c>
       <c r="B8" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>127778802</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127774280</v>
+        <v>127775915</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628702</v>
+        <v>628612</v>
       </c>
       <c r="R10" t="n">
-        <v>6918572</v>
+        <v>6918686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,45 +1564,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127778586</v>
+        <v>127774280</v>
       </c>
       <c r="B11" t="n">
-        <v>98373</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628451</v>
+        <v>628702</v>
       </c>
       <c r="R11" t="n">
-        <v>6918725</v>
+        <v>6918572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127775915</v>
+        <v>127777577</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,7 +1695,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1700,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628612</v>
+        <v>628305</v>
       </c>
       <c r="R12" t="n">
-        <v>6918686</v>
+        <v>6918693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,10 +1766,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127777577</v>
+        <v>127775315</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1796,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1801,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628305</v>
+        <v>628627</v>
       </c>
       <c r="R13" t="n">
-        <v>6918693</v>
+        <v>6918612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,49 +1867,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127775315</v>
+        <v>127778586</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628627</v>
+        <v>628451</v>
       </c>
       <c r="R14" t="n">
-        <v>6918612</v>
+        <v>6918725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,38 +1964,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777999</v>
+        <v>127776730</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>92630</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1435</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2004,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628284</v>
+        <v>628590</v>
       </c>
       <c r="R15" t="n">
-        <v>6918798</v>
+        <v>6918692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,11 +2044,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,42 +2070,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127776730</v>
+        <v>127777999</v>
       </c>
       <c r="B16" t="n">
-        <v>92627</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1435</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2115,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628590</v>
+        <v>628284</v>
       </c>
       <c r="R16" t="n">
-        <v>6918692</v>
+        <v>6918798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,6 +2146,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,7 +2180,7 @@
         <v>127778755</v>
       </c>
       <c r="B17" t="n">
-        <v>98490</v>
+        <v>98493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>127775800</v>
       </c>
       <c r="B18" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777111</v>
+        <v>127774703</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628453</v>
+        <v>628693</v>
       </c>
       <c r="R19" t="n">
-        <v>6918694</v>
+        <v>6918589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127774703</v>
+        <v>127777111</v>
       </c>
       <c r="B20" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>65</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628693</v>
+        <v>628453</v>
       </c>
       <c r="R20" t="n">
-        <v>6918589</v>
+        <v>6918694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
         <v>127775985</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127777244</v>
+        <v>127778761</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628416</v>
+        <v>628633</v>
       </c>
       <c r="R22" t="n">
-        <v>6918688</v>
+        <v>6918629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127778761</v>
+        <v>127777244</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628633</v>
+        <v>628416</v>
       </c>
       <c r="R23" t="n">
-        <v>6918629</v>
+        <v>6918688</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2884,7 +2884,7 @@
         <v>127777664</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127775318</v>
+        <v>127775258</v>
       </c>
       <c r="B25" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3089,10 +3089,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127776177</v>
+        <v>127776370</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>98493</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,28 +3100,24 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3164,11 +3160,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3195,10 +3186,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127776370</v>
+        <v>127776177</v>
       </c>
       <c r="B27" t="n">
-        <v>98490</v>
+        <v>98376</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,24 +3197,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3266,6 +3261,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127776178</v>
+        <v>127774870</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628598</v>
+        <v>628653</v>
       </c>
       <c r="R28" t="n">
-        <v>6918670</v>
+        <v>6918622</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127777628</v>
+        <v>127776178</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628304</v>
+        <v>628598</v>
       </c>
       <c r="R29" t="n">
-        <v>6918675</v>
+        <v>6918670</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127774870</v>
+        <v>127777628</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628653</v>
+        <v>628304</v>
       </c>
       <c r="R30" t="n">
-        <v>6918622</v>
+        <v>6918675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
         <v>127776816</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127777928</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127778213</v>
       </c>
       <c r="B33" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127775104</v>
       </c>
       <c r="B34" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127778222</v>
       </c>
       <c r="B35" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127778286</v>
       </c>
       <c r="B36" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>127776955</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>127776189</v>
       </c>
       <c r="B38" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>127777903</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,10 +4503,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127778769</v>
+        <v>127774928</v>
       </c>
       <c r="B40" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628626</v>
+        <v>628665</v>
       </c>
       <c r="R40" t="n">
-        <v>6918669</v>
+        <v>6918587</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127774928</v>
+        <v>127777102</v>
       </c>
       <c r="B41" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628665</v>
+        <v>628441</v>
       </c>
       <c r="R41" t="n">
-        <v>6918587</v>
+        <v>6918705</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127777102</v>
+        <v>127778769</v>
       </c>
       <c r="B42" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628441</v>
+        <v>628626</v>
       </c>
       <c r="R42" t="n">
-        <v>6918705</v>
+        <v>6918669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4797,7 +4797,7 @@
         <v>127774434</v>
       </c>
       <c r="B43" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127777316</v>
       </c>
       <c r="B44" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4996,37 +4996,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127776693</v>
+        <v>127778954</v>
       </c>
       <c r="B45" t="n">
-        <v>98456</v>
+        <v>92631</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5035,10 +5040,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628590</v>
+        <v>628675</v>
       </c>
       <c r="R45" t="n">
-        <v>6918692</v>
+        <v>6918656</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5097,10 +5102,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127774205</v>
+        <v>127777752</v>
       </c>
       <c r="B46" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5127,7 +5132,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5136,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628710</v>
+        <v>628353</v>
       </c>
       <c r="R46" t="n">
-        <v>6918574</v>
+        <v>6918711</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5172,11 +5177,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5203,42 +5203,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127778954</v>
+        <v>127775875</v>
       </c>
       <c r="B47" t="n">
-        <v>92628</v>
+        <v>98459</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5247,10 +5242,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628675</v>
+        <v>628595</v>
       </c>
       <c r="R47" t="n">
-        <v>6918656</v>
+        <v>6918652</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5283,6 +5278,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5312,7 +5312,7 @@
         <v>127774067</v>
       </c>
       <c r="B48" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>127775358</v>
       </c>
       <c r="B49" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5512,10 +5512,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127777752</v>
+        <v>127774205</v>
       </c>
       <c r="B50" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628353</v>
+        <v>628710</v>
       </c>
       <c r="R50" t="n">
-        <v>6918711</v>
+        <v>6918574</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,6 +5587,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5613,10 +5618,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127775875</v>
+        <v>127776693</v>
       </c>
       <c r="B51" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5643,7 +5648,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5652,10 +5657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628595</v>
+        <v>628590</v>
       </c>
       <c r="R51" t="n">
-        <v>6918652</v>
+        <v>6918692</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5688,11 +5693,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5722,7 +5722,7 @@
         <v>127774353</v>
       </c>
       <c r="B52" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>127834723</v>
       </c>
       <c r="B53" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>127836030</v>
       </c>
       <c r="B54" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>127836087</v>
       </c>
       <c r="B55" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>127833952</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>127834972</v>
       </c>
       <c r="B57" t="n">
-        <v>98490</v>
+        <v>98493</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127778500</v>
+        <v>127775382</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628416</v>
+        <v>628614</v>
       </c>
       <c r="R2" t="n">
-        <v>6918738</v>
+        <v>6918662</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,52 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775156</v>
+        <v>127774666</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628642</v>
+        <v>628697</v>
       </c>
       <c r="R3" t="n">
-        <v>6918602</v>
+        <v>6918580</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778961</v>
+        <v>127778500</v>
       </c>
       <c r="B4" t="n">
-        <v>97336</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628684</v>
+        <v>628416</v>
       </c>
       <c r="R4" t="n">
-        <v>6918685</v>
+        <v>6918738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,48 +970,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775382</v>
+        <v>127775156</v>
       </c>
       <c r="B5" t="n">
-        <v>98493</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628614</v>
+        <v>628642</v>
       </c>
       <c r="R5" t="n">
-        <v>6918662</v>
+        <v>6918602</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127774666</v>
+        <v>127778961</v>
       </c>
       <c r="B6" t="n">
-        <v>91341</v>
+        <v>97344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628697</v>
+        <v>628684</v>
       </c>
       <c r="R6" t="n">
-        <v>6918580</v>
+        <v>6918685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
         <v>127775456</v>
       </c>
       <c r="B7" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127774181</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>127778802</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127775915</v>
+        <v>127774280</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628612</v>
+        <v>628702</v>
       </c>
       <c r="R10" t="n">
-        <v>6918686</v>
+        <v>6918572</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127774280</v>
+        <v>127775915</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628702</v>
+        <v>628612</v>
       </c>
       <c r="R11" t="n">
-        <v>6918572</v>
+        <v>6918686</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
         <v>127777577</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>127775315</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>127778586</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,42 +1964,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127776730</v>
+        <v>127777999</v>
       </c>
       <c r="B15" t="n">
-        <v>92630</v>
+        <v>57669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1435</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2008,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628590</v>
+        <v>628284</v>
       </c>
       <c r="R15" t="n">
-        <v>6918692</v>
+        <v>6918798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,6 +2040,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2070,38 +2071,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127777999</v>
+        <v>127778755</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>98501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628284</v>
+        <v>628626</v>
       </c>
       <c r="R16" t="n">
-        <v>6918798</v>
+        <v>6918669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,11 +2146,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2177,37 +2172,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127778755</v>
+        <v>127776730</v>
       </c>
       <c r="B17" t="n">
-        <v>98493</v>
+        <v>92638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>1435</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628626</v>
+        <v>628590</v>
       </c>
       <c r="R17" t="n">
-        <v>6918669</v>
+        <v>6918692</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,7 +2281,7 @@
         <v>127775800</v>
       </c>
       <c r="B18" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>127774703</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127777111</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>127775985</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127778761</v>
+        <v>127777244</v>
       </c>
       <c r="B22" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628633</v>
+        <v>628416</v>
       </c>
       <c r="R22" t="n">
-        <v>6918629</v>
+        <v>6918688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127777244</v>
+        <v>127778761</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628416</v>
+        <v>628633</v>
       </c>
       <c r="R23" t="n">
-        <v>6918688</v>
+        <v>6918629</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2881,50 +2881,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127777664</v>
+        <v>127776370</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>98501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628294</v>
+        <v>628595</v>
       </c>
       <c r="R24" t="n">
-        <v>6918677</v>
+        <v>6918652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2988,37 +2978,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127775258</v>
+        <v>127776177</v>
       </c>
       <c r="B25" t="n">
-        <v>98459</v>
+        <v>98384</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3027,10 +3017,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628620</v>
+        <v>628595</v>
       </c>
       <c r="R25" t="n">
-        <v>6918640</v>
+        <v>6918652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3063,6 +3053,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3089,45 +3084,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127776370</v>
+        <v>127775258</v>
       </c>
       <c r="B26" t="n">
-        <v>98493</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628595</v>
+        <v>628620</v>
       </c>
       <c r="R26" t="n">
-        <v>6918652</v>
+        <v>6918640</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3186,37 +3185,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127776177</v>
+        <v>127777664</v>
       </c>
       <c r="B27" t="n">
-        <v>98376</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628595</v>
+        <v>628294</v>
       </c>
       <c r="R27" t="n">
-        <v>6918652</v>
+        <v>6918677</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Förekommer inom våt området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3295,7 +3295,7 @@
         <v>127774870</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127776178</v>
+        <v>127777628</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628598</v>
+        <v>628304</v>
       </c>
       <c r="R29" t="n">
-        <v>6918670</v>
+        <v>6918675</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127777628</v>
+        <v>127776178</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628304</v>
+        <v>628598</v>
       </c>
       <c r="R30" t="n">
-        <v>6918675</v>
+        <v>6918670</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
         <v>127776816</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127777928</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127778213</v>
       </c>
       <c r="B33" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127775104</v>
       </c>
       <c r="B34" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127778222</v>
       </c>
       <c r="B35" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,37 +4097,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127778286</v>
+        <v>127776955</v>
       </c>
       <c r="B36" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>44</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4136,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628333</v>
+        <v>628471</v>
       </c>
       <c r="R36" t="n">
-        <v>6918773</v>
+        <v>6918667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,6 +4173,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,38 +4204,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127776955</v>
+        <v>127778286</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>44</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4238,10 +4243,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628471</v>
+        <v>628333</v>
       </c>
       <c r="R37" t="n">
-        <v>6918667</v>
+        <v>6918773</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,11 +4279,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,7 +4308,7 @@
         <v>127776189</v>
       </c>
       <c r="B38" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>127777903</v>
       </c>
       <c r="B39" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,10 +4503,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127774928</v>
+        <v>127778769</v>
       </c>
       <c r="B40" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628665</v>
+        <v>628626</v>
       </c>
       <c r="R40" t="n">
-        <v>6918587</v>
+        <v>6918669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127777102</v>
+        <v>127774928</v>
       </c>
       <c r="B41" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628441</v>
+        <v>628665</v>
       </c>
       <c r="R41" t="n">
-        <v>6918705</v>
+        <v>6918587</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127778769</v>
+        <v>127777102</v>
       </c>
       <c r="B42" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628626</v>
+        <v>628441</v>
       </c>
       <c r="R42" t="n">
-        <v>6918669</v>
+        <v>6918705</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4797,7 +4797,7 @@
         <v>127774434</v>
       </c>
       <c r="B43" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127777316</v>
       </c>
       <c r="B44" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>127778954</v>
       </c>
       <c r="B45" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,10 +5102,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127777752</v>
+        <v>127776693</v>
       </c>
       <c r="B46" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628353</v>
+        <v>628590</v>
       </c>
       <c r="R46" t="n">
-        <v>6918711</v>
+        <v>6918692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127775875</v>
+        <v>127775358</v>
       </c>
       <c r="B47" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5242,10 +5242,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628595</v>
+        <v>628614</v>
       </c>
       <c r="R47" t="n">
-        <v>6918652</v>
+        <v>6918662</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5278,11 +5278,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5309,38 +5304,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127774067</v>
+        <v>127774205</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>98467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5349,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628716</v>
+        <v>628710</v>
       </c>
       <c r="R48" t="n">
-        <v>6918568</v>
+        <v>6918574</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5385,6 +5379,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5411,10 +5410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127775358</v>
+        <v>127777752</v>
       </c>
       <c r="B49" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5441,7 +5440,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5450,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628614</v>
+        <v>628353</v>
       </c>
       <c r="R49" t="n">
-        <v>6918662</v>
+        <v>6918711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5512,10 +5511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127774205</v>
+        <v>127775875</v>
       </c>
       <c r="B50" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5542,7 +5541,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5551,10 +5550,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628710</v>
+        <v>628595</v>
       </c>
       <c r="R50" t="n">
-        <v>6918574</v>
+        <v>6918652</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5591,7 +5590,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Påväg att blomma</t>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5618,37 +5617,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127776693</v>
+        <v>127774067</v>
       </c>
       <c r="B51" t="n">
-        <v>98459</v>
+        <v>57832</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628590</v>
+        <v>628716</v>
       </c>
       <c r="R51" t="n">
-        <v>6918692</v>
+        <v>6918568</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5722,7 +5722,7 @@
         <v>127774353</v>
       </c>
       <c r="B52" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>127834723</v>
       </c>
       <c r="B53" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>127836030</v>
       </c>
       <c r="B54" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>127836087</v>
       </c>
       <c r="B55" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>127833952</v>
       </c>
       <c r="B56" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>127834972</v>
       </c>
       <c r="B57" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127775382</v>
+        <v>127774666</v>
       </c>
       <c r="B2" t="n">
-        <v>98501</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628614</v>
+        <v>628697</v>
       </c>
       <c r="R2" t="n">
-        <v>6918662</v>
+        <v>6918580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127774666</v>
+        <v>127778961</v>
       </c>
       <c r="B3" t="n">
-        <v>91349</v>
+        <v>97345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628697</v>
+        <v>628684</v>
       </c>
       <c r="R3" t="n">
-        <v>6918580</v>
+        <v>6918685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,49 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778500</v>
+        <v>127775382</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628416</v>
+        <v>628614</v>
       </c>
       <c r="R4" t="n">
-        <v>6918738</v>
+        <v>6918662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775156</v>
+        <v>127778500</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,7 +996,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1009,13 +1005,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628642</v>
+        <v>628416</v>
       </c>
       <c r="R5" t="n">
-        <v>6918602</v>
+        <v>6918738</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,48 +1067,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778961</v>
+        <v>127775156</v>
       </c>
       <c r="B6" t="n">
-        <v>97344</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628684</v>
+        <v>628642</v>
       </c>
       <c r="R6" t="n">
-        <v>6918685</v>
+        <v>6918602</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127775456</v>
       </c>
       <c r="B7" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127774181</v>
       </c>
       <c r="B8" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>127778802</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,49 +1463,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127774280</v>
+        <v>127778586</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628702</v>
+        <v>628451</v>
       </c>
       <c r="R10" t="n">
-        <v>6918572</v>
+        <v>6918725</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,7 +1563,7 @@
         <v>127775915</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127777577</v>
+        <v>127774280</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1691,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1704,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628305</v>
+        <v>628702</v>
       </c>
       <c r="R12" t="n">
-        <v>6918693</v>
+        <v>6918572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127775315</v>
+        <v>127777577</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,7 +1792,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1805,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628627</v>
+        <v>628305</v>
       </c>
       <c r="R13" t="n">
-        <v>6918612</v>
+        <v>6918693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,45 +1863,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127778586</v>
+        <v>127775315</v>
       </c>
       <c r="B14" t="n">
-        <v>98384</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628451</v>
+        <v>628627</v>
       </c>
       <c r="R14" t="n">
-        <v>6918725</v>
+        <v>6918612</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,38 +1964,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127777999</v>
+        <v>127776730</v>
       </c>
       <c r="B15" t="n">
-        <v>57669</v>
+        <v>92639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1435</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2004,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628284</v>
+        <v>628590</v>
       </c>
       <c r="R15" t="n">
-        <v>6918798</v>
+        <v>6918692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,11 +2044,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,37 +2070,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127778755</v>
+        <v>127777999</v>
       </c>
       <c r="B16" t="n">
-        <v>98501</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628626</v>
+        <v>628284</v>
       </c>
       <c r="R16" t="n">
-        <v>6918669</v>
+        <v>6918798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,6 +2146,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,42 +2177,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127776730</v>
+        <v>127778755</v>
       </c>
       <c r="B17" t="n">
-        <v>92638</v>
+        <v>98502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1435</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628590</v>
+        <v>628626</v>
       </c>
       <c r="R17" t="n">
-        <v>6918692</v>
+        <v>6918669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,45 +2278,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127775800</v>
+        <v>127777111</v>
       </c>
       <c r="B18" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628598</v>
+        <v>628453</v>
       </c>
       <c r="R18" t="n">
-        <v>6918637</v>
+        <v>6918694</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,49 +2379,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127774703</v>
+        <v>127775800</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628693</v>
+        <v>628598</v>
       </c>
       <c r="R19" t="n">
-        <v>6918589</v>
+        <v>6918637</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777111</v>
+        <v>127774703</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628453</v>
+        <v>628693</v>
       </c>
       <c r="R20" t="n">
-        <v>6918694</v>
+        <v>6918589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,7 +2682,7 @@
         <v>127777244</v>
       </c>
       <c r="B22" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>127778761</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2881,45 +2881,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127776370</v>
+        <v>127777664</v>
       </c>
       <c r="B24" t="n">
-        <v>98501</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628595</v>
+        <v>628294</v>
       </c>
       <c r="R24" t="n">
-        <v>6918652</v>
+        <v>6918677</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,6 +2957,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2978,37 +2988,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776177</v>
+        <v>127775258</v>
       </c>
       <c r="B25" t="n">
-        <v>98384</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3017,10 +3027,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628595</v>
+        <v>628620</v>
       </c>
       <c r="R25" t="n">
-        <v>6918652</v>
+        <v>6918640</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3053,11 +3063,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3084,49 +3089,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127775258</v>
+        <v>127776370</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>98502</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628620</v>
+        <v>628595</v>
       </c>
       <c r="R26" t="n">
-        <v>6918640</v>
+        <v>6918652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,38 +3186,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127777664</v>
+        <v>127776177</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628294</v>
+        <v>628595</v>
       </c>
       <c r="R27" t="n">
-        <v>6918677</v>
+        <v>6918652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3295,7 +3295,7 @@
         <v>127774870</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127777628</v>
+        <v>127776178</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628304</v>
+        <v>628598</v>
       </c>
       <c r="R29" t="n">
-        <v>6918675</v>
+        <v>6918670</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127776178</v>
+        <v>127777628</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628598</v>
+        <v>628304</v>
       </c>
       <c r="R30" t="n">
-        <v>6918670</v>
+        <v>6918675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
         <v>127776816</v>
       </c>
       <c r="B31" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127777928</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127778213</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127775104</v>
       </c>
       <c r="B34" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127778222</v>
       </c>
       <c r="B35" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>127778286</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>127776189</v>
       </c>
       <c r="B38" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>127777903</v>
       </c>
       <c r="B39" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>127778769</v>
       </c>
       <c r="B40" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>127774928</v>
       </c>
       <c r="B41" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127777102</v>
       </c>
       <c r="B42" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127774434</v>
+        <v>127777316</v>
       </c>
       <c r="B43" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628697</v>
+        <v>628396</v>
       </c>
       <c r="R43" t="n">
-        <v>6918580</v>
+        <v>6918706</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127777316</v>
+        <v>127774434</v>
       </c>
       <c r="B44" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628396</v>
+        <v>628697</v>
       </c>
       <c r="R44" t="n">
-        <v>6918706</v>
+        <v>6918580</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4999,7 +4999,7 @@
         <v>127778954</v>
       </c>
       <c r="B45" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,37 +5102,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127776693</v>
+        <v>127774067</v>
       </c>
       <c r="B46" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5141,10 +5142,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628590</v>
+        <v>628716</v>
       </c>
       <c r="R46" t="n">
-        <v>6918692</v>
+        <v>6918568</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5203,10 +5204,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127775358</v>
+        <v>127774205</v>
       </c>
       <c r="B47" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5233,7 +5234,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5242,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628614</v>
+        <v>628710</v>
       </c>
       <c r="R47" t="n">
-        <v>6918662</v>
+        <v>6918574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5278,6 +5279,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5304,10 +5310,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127774205</v>
+        <v>127775358</v>
       </c>
       <c r="B48" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,7 +5340,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5343,10 +5349,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628710</v>
+        <v>628614</v>
       </c>
       <c r="R48" t="n">
-        <v>6918574</v>
+        <v>6918662</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5379,11 +5385,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5413,7 +5414,7 @@
         <v>127777752</v>
       </c>
       <c r="B49" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5511,10 +5512,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127775875</v>
+        <v>127776693</v>
       </c>
       <c r="B50" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5541,7 +5542,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5550,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628595</v>
+        <v>628590</v>
       </c>
       <c r="R50" t="n">
-        <v>6918652</v>
+        <v>6918692</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5586,11 +5587,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5617,38 +5613,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127774067</v>
+        <v>127775875</v>
       </c>
       <c r="B51" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5657,10 +5652,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628716</v>
+        <v>628595</v>
       </c>
       <c r="R51" t="n">
-        <v>6918568</v>
+        <v>6918652</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5693,6 +5688,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5722,7 +5722,7 @@
         <v>127774353</v>
       </c>
       <c r="B52" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>127834723</v>
       </c>
       <c r="B53" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>127836030</v>
       </c>
       <c r="B54" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>127836087</v>
       </c>
       <c r="B55" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>127834972</v>
       </c>
       <c r="B57" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -869,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127775382</v>
+        <v>127778500</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628614</v>
+        <v>628416</v>
       </c>
       <c r="R4" t="n">
-        <v>6918662</v>
+        <v>6918738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127778500</v>
+        <v>127775382</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628416</v>
+        <v>628614</v>
       </c>
       <c r="R5" t="n">
-        <v>6918738</v>
+        <v>6918662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2278,49 +2278,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127777111</v>
+        <v>127775800</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>91350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628453</v>
+        <v>628598</v>
       </c>
       <c r="R18" t="n">
-        <v>6918694</v>
+        <v>6918637</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,45 +2375,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127775800</v>
+        <v>127774703</v>
       </c>
       <c r="B19" t="n">
-        <v>91350</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628598</v>
+        <v>628693</v>
       </c>
       <c r="R19" t="n">
-        <v>6918637</v>
+        <v>6918589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127774703</v>
+        <v>127777111</v>
       </c>
       <c r="B20" t="n">
         <v>98468</v>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>65</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628693</v>
+        <v>628453</v>
       </c>
       <c r="R20" t="n">
-        <v>6918589</v>
+        <v>6918694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127777928</v>
+        <v>127778213</v>
       </c>
       <c r="B32" t="n">
         <v>98468</v>
@@ -3726,7 +3726,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3735,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628289</v>
+        <v>628284</v>
       </c>
       <c r="R32" t="n">
-        <v>6918777</v>
+        <v>6918798</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3797,7 +3802,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127778213</v>
+        <v>127777928</v>
       </c>
       <c r="B33" t="n">
         <v>98468</v>
@@ -3827,12 +3832,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628284</v>
+        <v>628289</v>
       </c>
       <c r="R33" t="n">
-        <v>6918798</v>
+        <v>6918777</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127777316</v>
+        <v>127774434</v>
       </c>
       <c r="B43" t="n">
         <v>98468</v>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628396</v>
+        <v>628697</v>
       </c>
       <c r="R43" t="n">
-        <v>6918706</v>
+        <v>6918580</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4895,7 +4895,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127774434</v>
+        <v>127777316</v>
       </c>
       <c r="B44" t="n">
         <v>98468</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628697</v>
+        <v>628396</v>
       </c>
       <c r="R44" t="n">
-        <v>6918580</v>
+        <v>6918706</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127774205</v>
+        <v>127775358</v>
       </c>
       <c r="B47" t="n">
         <v>98468</v>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628710</v>
+        <v>628614</v>
       </c>
       <c r="R47" t="n">
-        <v>6918574</v>
+        <v>6918662</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5279,11 +5279,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5310,7 +5305,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127775358</v>
+        <v>127777752</v>
       </c>
       <c r="B48" t="n">
         <v>98468</v>
@@ -5340,7 +5335,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5349,10 +5344,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628614</v>
+        <v>628353</v>
       </c>
       <c r="R48" t="n">
-        <v>6918662</v>
+        <v>6918711</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5411,7 +5406,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127777752</v>
+        <v>127774205</v>
       </c>
       <c r="B49" t="n">
         <v>98468</v>
@@ -5441,7 +5436,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5450,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628353</v>
+        <v>628710</v>
       </c>
       <c r="R49" t="n">
-        <v>6918711</v>
+        <v>6918574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,6 +5481,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127774666</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127778961</v>
+        <v>127778500</v>
       </c>
       <c r="B3" t="n">
-        <v>97345</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628684</v>
+        <v>628416</v>
       </c>
       <c r="R3" t="n">
-        <v>6918685</v>
+        <v>6918738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778500</v>
+        <v>127775382</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628416</v>
+        <v>628614</v>
       </c>
       <c r="R4" t="n">
-        <v>6918738</v>
+        <v>6918662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,48 +970,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775382</v>
+        <v>127775156</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628614</v>
+        <v>628642</v>
       </c>
       <c r="R5" t="n">
-        <v>6918662</v>
+        <v>6918602</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,52 +1071,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775156</v>
+        <v>127778961</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>97346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628642</v>
+        <v>628684</v>
       </c>
       <c r="R6" t="n">
-        <v>6918602</v>
+        <v>6918685</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127775456</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127774181</v>
       </c>
       <c r="B8" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>127778802</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,45 +1463,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778586</v>
+        <v>127774280</v>
       </c>
       <c r="B10" t="n">
-        <v>98385</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628451</v>
+        <v>628702</v>
       </c>
       <c r="R10" t="n">
-        <v>6918725</v>
+        <v>6918572</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1567,7 @@
         <v>127775915</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127774280</v>
+        <v>127777577</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,7 +1695,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1700,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628702</v>
+        <v>628305</v>
       </c>
       <c r="R12" t="n">
-        <v>6918572</v>
+        <v>6918693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,10 +1766,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127777577</v>
+        <v>127775315</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,7 +1796,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1801,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628305</v>
+        <v>628627</v>
       </c>
       <c r="R13" t="n">
-        <v>6918693</v>
+        <v>6918612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,49 +1867,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127775315</v>
+        <v>127778586</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628627</v>
+        <v>628451</v>
       </c>
       <c r="R14" t="n">
-        <v>6918612</v>
+        <v>6918725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>127776730</v>
       </c>
       <c r="B15" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>127778755</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>127775800</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>127774703</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127777111</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>127777244</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>127778761</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127775258</v>
+        <v>127775318</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3092,7 +3092,7 @@
         <v>127776370</v>
       </c>
       <c r="B26" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>127776177</v>
       </c>
       <c r="B27" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127774870</v>
+        <v>127777628</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628653</v>
+        <v>628304</v>
       </c>
       <c r="R28" t="n">
-        <v>6918622</v>
+        <v>6918675</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127776178</v>
+        <v>127774870</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628598</v>
+        <v>628653</v>
       </c>
       <c r="R29" t="n">
-        <v>6918670</v>
+        <v>6918622</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127777628</v>
+        <v>127776178</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628304</v>
+        <v>628598</v>
       </c>
       <c r="R30" t="n">
-        <v>6918675</v>
+        <v>6918670</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
         <v>127776816</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127778213</v>
+        <v>127777928</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3726,12 +3726,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3740,10 +3735,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628284</v>
+        <v>628289</v>
       </c>
       <c r="R32" t="n">
-        <v>6918798</v>
+        <v>6918777</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3802,10 +3797,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127777928</v>
+        <v>127778213</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,7 +3827,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628289</v>
+        <v>628284</v>
       </c>
       <c r="R33" t="n">
-        <v>6918777</v>
+        <v>6918798</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
         <v>127775104</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127778222</v>
       </c>
       <c r="B35" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,38 +4097,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127776955</v>
+        <v>127778286</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>44</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4137,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628471</v>
+        <v>628333</v>
       </c>
       <c r="R36" t="n">
-        <v>6918667</v>
+        <v>6918773</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,11 +4172,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4204,37 +4198,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127778286</v>
+        <v>127776955</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>44</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4243,10 +4238,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628333</v>
+        <v>628471</v>
       </c>
       <c r="R37" t="n">
-        <v>6918773</v>
+        <v>6918667</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,6 +4274,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,7 +4308,7 @@
         <v>127776189</v>
       </c>
       <c r="B38" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>127777903</v>
       </c>
       <c r="B39" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>127778769</v>
       </c>
       <c r="B40" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>127774928</v>
       </c>
       <c r="B41" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127777102</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>127774434</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127777316</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>127778954</v>
       </c>
       <c r="B45" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,38 +5102,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127774067</v>
+        <v>127776693</v>
       </c>
       <c r="B46" t="n">
-        <v>57832</v>
+        <v>98469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5142,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628716</v>
+        <v>628590</v>
       </c>
       <c r="R46" t="n">
-        <v>6918568</v>
+        <v>6918692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5207,7 +5206,7 @@
         <v>127775358</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,10 +5304,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127777752</v>
+        <v>127775875</v>
       </c>
       <c r="B48" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5335,7 +5334,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5344,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628353</v>
+        <v>628595</v>
       </c>
       <c r="R48" t="n">
-        <v>6918711</v>
+        <v>6918652</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5380,6 +5379,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5406,37 +5410,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127774205</v>
+        <v>127774067</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>57832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5445,10 +5450,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628710</v>
+        <v>628716</v>
       </c>
       <c r="R49" t="n">
-        <v>6918574</v>
+        <v>6918568</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,11 +5486,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5512,10 +5512,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127776693</v>
+        <v>127774205</v>
       </c>
       <c r="B50" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628590</v>
+        <v>628710</v>
       </c>
       <c r="R50" t="n">
-        <v>6918692</v>
+        <v>6918574</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,6 +5587,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5613,10 +5618,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127775875</v>
+        <v>127777752</v>
       </c>
       <c r="B51" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5643,7 +5648,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5652,10 +5657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628595</v>
+        <v>628353</v>
       </c>
       <c r="R51" t="n">
-        <v>6918652</v>
+        <v>6918711</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5688,11 +5693,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5722,7 +5722,7 @@
         <v>127774353</v>
       </c>
       <c r="B52" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>127834723</v>
       </c>
       <c r="B53" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>127836030</v>
       </c>
       <c r="B54" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>127836087</v>
       </c>
       <c r="B55" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>127834972</v>
       </c>
       <c r="B57" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127774666</v>
       </c>
       <c r="B2" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127778500</v>
+        <v>127775382</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628416</v>
+        <v>628614</v>
       </c>
       <c r="R3" t="n">
-        <v>6918738</v>
+        <v>6918662</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127775382</v>
+        <v>127778500</v>
       </c>
       <c r="B4" t="n">
-        <v>98503</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628614</v>
+        <v>628416</v>
       </c>
       <c r="R4" t="n">
-        <v>6918662</v>
+        <v>6918738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
         <v>127775156</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>127778961</v>
       </c>
       <c r="B6" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127775456</v>
       </c>
       <c r="B7" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127774181</v>
       </c>
       <c r="B8" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>127778802</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,49 +1463,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127774280</v>
+        <v>127778586</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>98387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628702</v>
+        <v>628451</v>
       </c>
       <c r="R10" t="n">
-        <v>6918572</v>
+        <v>6918725</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,7 +1563,7 @@
         <v>127775915</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127777577</v>
+        <v>127774280</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1691,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1704,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628305</v>
+        <v>628702</v>
       </c>
       <c r="R12" t="n">
-        <v>6918693</v>
+        <v>6918572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127775315</v>
+        <v>127777577</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,7 +1792,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1805,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628627</v>
+        <v>628305</v>
       </c>
       <c r="R13" t="n">
-        <v>6918612</v>
+        <v>6918693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,45 +1863,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127778586</v>
+        <v>127775315</v>
       </c>
       <c r="B14" t="n">
-        <v>98386</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628451</v>
+        <v>628627</v>
       </c>
       <c r="R14" t="n">
-        <v>6918725</v>
+        <v>6918612</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>127776730</v>
       </c>
       <c r="B15" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>127778755</v>
       </c>
       <c r="B17" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,45 +2278,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127775800</v>
+        <v>127774703</v>
       </c>
       <c r="B18" t="n">
-        <v>91351</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628598</v>
+        <v>628693</v>
       </c>
       <c r="R18" t="n">
-        <v>6918637</v>
+        <v>6918589</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127774703</v>
+        <v>127777111</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,7 +2409,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>65</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2414,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628693</v>
+        <v>628453</v>
       </c>
       <c r="R19" t="n">
-        <v>6918589</v>
+        <v>6918694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,49 +2480,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127777111</v>
+        <v>127775800</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>91352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628453</v>
+        <v>628598</v>
       </c>
       <c r="R20" t="n">
-        <v>6918694</v>
+        <v>6918637</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,7 +2682,7 @@
         <v>127777244</v>
       </c>
       <c r="B22" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>127778761</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127775318</v>
+        <v>127775258</v>
       </c>
       <c r="B25" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3092,7 +3092,7 @@
         <v>127776370</v>
       </c>
       <c r="B26" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>127776177</v>
       </c>
       <c r="B27" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127777628</v>
+        <v>127774870</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628304</v>
+        <v>628653</v>
       </c>
       <c r="R28" t="n">
-        <v>6918675</v>
+        <v>6918622</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127774870</v>
+        <v>127776178</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628653</v>
+        <v>628598</v>
       </c>
       <c r="R29" t="n">
-        <v>6918622</v>
+        <v>6918670</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127776178</v>
+        <v>127777628</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628598</v>
+        <v>628304</v>
       </c>
       <c r="R30" t="n">
-        <v>6918670</v>
+        <v>6918675</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
         <v>127776816</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127777928</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127778213</v>
       </c>
       <c r="B33" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127775104</v>
       </c>
       <c r="B34" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127778222</v>
       </c>
       <c r="B35" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,37 +4097,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127778286</v>
+        <v>127776955</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>44</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4136,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628333</v>
+        <v>628471</v>
       </c>
       <c r="R36" t="n">
-        <v>6918773</v>
+        <v>6918667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,6 +4173,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,38 +4204,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127776955</v>
+        <v>127778286</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>44</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4238,10 +4243,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628471</v>
+        <v>628333</v>
       </c>
       <c r="R37" t="n">
-        <v>6918667</v>
+        <v>6918773</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,11 +4279,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,7 +4308,7 @@
         <v>127776189</v>
       </c>
       <c r="B38" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>127777903</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>127778769</v>
       </c>
       <c r="B40" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>127774928</v>
       </c>
       <c r="B41" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127777102</v>
       </c>
       <c r="B42" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>127774434</v>
       </c>
       <c r="B43" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127777316</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>127778954</v>
       </c>
       <c r="B45" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5102,10 +5102,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127776693</v>
+        <v>127775358</v>
       </c>
       <c r="B46" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628590</v>
+        <v>628614</v>
       </c>
       <c r="R46" t="n">
-        <v>6918692</v>
+        <v>6918662</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127775358</v>
+        <v>127777752</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5242,10 +5242,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628614</v>
+        <v>628353</v>
       </c>
       <c r="R47" t="n">
-        <v>6918662</v>
+        <v>6918711</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5304,10 +5304,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127775875</v>
+        <v>127774205</v>
       </c>
       <c r="B48" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628595</v>
+        <v>628710</v>
       </c>
       <c r="R48" t="n">
-        <v>6918652</v>
+        <v>6918574</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5410,38 +5410,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127774067</v>
+        <v>127776693</v>
       </c>
       <c r="B49" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5450,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628716</v>
+        <v>628590</v>
       </c>
       <c r="R49" t="n">
-        <v>6918568</v>
+        <v>6918692</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5512,10 +5511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127774205</v>
+        <v>127775875</v>
       </c>
       <c r="B50" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5542,7 +5541,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5551,10 +5550,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628710</v>
+        <v>628595</v>
       </c>
       <c r="R50" t="n">
-        <v>6918574</v>
+        <v>6918652</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5591,7 +5590,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Påväg att blomma</t>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5618,37 +5617,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127777752</v>
+        <v>127774067</v>
       </c>
       <c r="B51" t="n">
-        <v>98469</v>
+        <v>57832</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628353</v>
+        <v>628716</v>
       </c>
       <c r="R51" t="n">
-        <v>6918711</v>
+        <v>6918568</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5722,7 +5722,7 @@
         <v>127774353</v>
       </c>
       <c r="B52" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>127834723</v>
       </c>
       <c r="B53" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>127836030</v>
       </c>
       <c r="B54" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>127836087</v>
       </c>
       <c r="B55" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6111,48 +6111,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127833952</v>
+        <v>127834972</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>98504</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupmyran, Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628647</v>
+        <v>628267</v>
       </c>
       <c r="R56" t="n">
-        <v>6918692</v>
+        <v>6918732</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6193,7 +6190,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6212,45 +6208,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127834972</v>
+        <v>127833952</v>
       </c>
       <c r="B57" t="n">
-        <v>98503</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Djupmyran, Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628267</v>
+        <v>628647</v>
       </c>
       <c r="R57" t="n">
-        <v>6918732</v>
+        <v>6918692</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6291,6 +6290,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -970,52 +970,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775156</v>
+        <v>127778961</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628642</v>
+        <v>628684</v>
       </c>
       <c r="R5" t="n">
-        <v>6918602</v>
+        <v>6918685</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,48 +1067,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778961</v>
+        <v>127775156</v>
       </c>
       <c r="B6" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628684</v>
+        <v>628642</v>
       </c>
       <c r="R6" t="n">
-        <v>6918685</v>
+        <v>6918602</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,45 +1265,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127774181</v>
+        <v>127778802</v>
       </c>
       <c r="B8" t="n">
-        <v>91317</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628716</v>
+        <v>628634</v>
       </c>
       <c r="R8" t="n">
-        <v>6918568</v>
+        <v>6918656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,49 +1366,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127778802</v>
+        <v>127774181</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>91317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628634</v>
+        <v>628716</v>
       </c>
       <c r="R9" t="n">
-        <v>6918656</v>
+        <v>6918568</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,45 +1463,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778586</v>
+        <v>127775915</v>
       </c>
       <c r="B10" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628451</v>
+        <v>628612</v>
       </c>
       <c r="R10" t="n">
-        <v>6918725</v>
+        <v>6918686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,7 +1564,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127775915</v>
+        <v>127774280</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1590,7 +1594,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1599,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628612</v>
+        <v>628702</v>
       </c>
       <c r="R11" t="n">
-        <v>6918686</v>
+        <v>6918572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,7 +1665,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127774280</v>
+        <v>127777577</v>
       </c>
       <c r="B12" t="n">
         <v>98470</v>
@@ -1691,7 +1695,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1700,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628702</v>
+        <v>628305</v>
       </c>
       <c r="R12" t="n">
-        <v>6918572</v>
+        <v>6918693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1766,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127777577</v>
+        <v>127775315</v>
       </c>
       <c r="B13" t="n">
         <v>98470</v>
@@ -1792,7 +1796,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1801,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628305</v>
+        <v>628627</v>
       </c>
       <c r="R13" t="n">
-        <v>6918693</v>
+        <v>6918612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,49 +1867,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127775315</v>
+        <v>127778586</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628627</v>
+        <v>628451</v>
       </c>
       <c r="R14" t="n">
-        <v>6918612</v>
+        <v>6918725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,42 +1964,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127776730</v>
+        <v>127778755</v>
       </c>
       <c r="B15" t="n">
-        <v>92641</v>
+        <v>98504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1435</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2008,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628590</v>
+        <v>628626</v>
       </c>
       <c r="R15" t="n">
-        <v>6918692</v>
+        <v>6918669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,38 +2065,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127777999</v>
+        <v>127776730</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>92641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1435</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2110,10 +2109,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628284</v>
+        <v>628590</v>
       </c>
       <c r="R16" t="n">
-        <v>6918798</v>
+        <v>6918692</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,11 +2145,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2177,37 +2171,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127778755</v>
+        <v>127777999</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2216,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628626</v>
+        <v>628284</v>
       </c>
       <c r="R17" t="n">
-        <v>6918669</v>
+        <v>6918798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,6 +2247,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2278,49 +2278,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127774703</v>
+        <v>127775800</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628693</v>
+        <v>628598</v>
       </c>
       <c r="R18" t="n">
-        <v>6918589</v>
+        <v>6918637</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,7 +2375,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127777111</v>
+        <v>127774703</v>
       </c>
       <c r="B19" t="n">
         <v>98470</v>
@@ -2409,7 +2405,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2418,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628453</v>
+        <v>628693</v>
       </c>
       <c r="R19" t="n">
-        <v>6918694</v>
+        <v>6918589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,45 +2476,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127775800</v>
+        <v>127777111</v>
       </c>
       <c r="B20" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628598</v>
+        <v>628453</v>
       </c>
       <c r="R20" t="n">
-        <v>6918637</v>
+        <v>6918694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2881,50 +2881,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127777664</v>
+        <v>127776370</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628294</v>
+        <v>628595</v>
       </c>
       <c r="R24" t="n">
-        <v>6918677</v>
+        <v>6918652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2988,37 +2978,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127775258</v>
+        <v>127776177</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3027,10 +3017,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628620</v>
+        <v>628595</v>
       </c>
       <c r="R25" t="n">
-        <v>6918640</v>
+        <v>6918652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3063,6 +3053,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3089,45 +3084,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127776370</v>
+        <v>127775258</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628595</v>
+        <v>628620</v>
       </c>
       <c r="R26" t="n">
-        <v>6918652</v>
+        <v>6918640</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3186,37 +3185,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127776177</v>
+        <v>127777664</v>
       </c>
       <c r="B27" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628595</v>
+        <v>628294</v>
       </c>
       <c r="R27" t="n">
-        <v>6918652</v>
+        <v>6918677</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Förekommer inom våt området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4503,7 +4503,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127778769</v>
+        <v>127774928</v>
       </c>
       <c r="B40" t="n">
         <v>91352</v>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628626</v>
+        <v>628665</v>
       </c>
       <c r="R40" t="n">
-        <v>6918669</v>
+        <v>6918587</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127774928</v>
+        <v>127777102</v>
       </c>
       <c r="B41" t="n">
         <v>91352</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628665</v>
+        <v>628441</v>
       </c>
       <c r="R41" t="n">
-        <v>6918587</v>
+        <v>6918705</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127777102</v>
+        <v>127778769</v>
       </c>
       <c r="B42" t="n">
         <v>91352</v>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628441</v>
+        <v>628626</v>
       </c>
       <c r="R42" t="n">
-        <v>6918705</v>
+        <v>6918669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5102,37 +5102,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127775358</v>
+        <v>127774067</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5141,10 +5142,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628614</v>
+        <v>628716</v>
       </c>
       <c r="R46" t="n">
-        <v>6918662</v>
+        <v>6918568</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5203,7 +5204,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127777752</v>
+        <v>127775358</v>
       </c>
       <c r="B47" t="n">
         <v>98470</v>
@@ -5233,7 +5234,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5242,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628353</v>
+        <v>628614</v>
       </c>
       <c r="R47" t="n">
-        <v>6918711</v>
+        <v>6918662</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5304,7 +5305,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127774205</v>
+        <v>127777752</v>
       </c>
       <c r="B48" t="n">
         <v>98470</v>
@@ -5334,7 +5335,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5343,10 +5344,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628710</v>
+        <v>628353</v>
       </c>
       <c r="R48" t="n">
-        <v>6918574</v>
+        <v>6918711</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5379,11 +5380,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5410,7 +5406,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127776693</v>
+        <v>127774205</v>
       </c>
       <c r="B49" t="n">
         <v>98470</v>
@@ -5440,7 +5436,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5449,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628590</v>
+        <v>628710</v>
       </c>
       <c r="R49" t="n">
-        <v>6918692</v>
+        <v>6918574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5485,6 +5481,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5511,7 +5512,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127775875</v>
+        <v>127776693</v>
       </c>
       <c r="B50" t="n">
         <v>98470</v>
@@ -5541,7 +5542,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5550,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628595</v>
+        <v>628590</v>
       </c>
       <c r="R50" t="n">
-        <v>6918652</v>
+        <v>6918692</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5586,11 +5587,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5617,38 +5613,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127774067</v>
+        <v>127775875</v>
       </c>
       <c r="B51" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5657,10 +5652,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628716</v>
+        <v>628595</v>
       </c>
       <c r="R51" t="n">
-        <v>6918568</v>
+        <v>6918652</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5693,6 +5688,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6111,45 +6111,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127834972</v>
+        <v>127833952</v>
       </c>
       <c r="B56" t="n">
-        <v>98504</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupmyran, Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628267</v>
+        <v>628647</v>
       </c>
       <c r="R56" t="n">
-        <v>6918732</v>
+        <v>6918692</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6190,6 +6193,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6208,48 +6212,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127833952</v>
+        <v>127834972</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>98504</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Djupmyran, Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628647</v>
+        <v>628267</v>
       </c>
       <c r="R57" t="n">
-        <v>6918692</v>
+        <v>6918732</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6290,7 +6291,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -1964,37 +1964,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127778755</v>
+        <v>127776730</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>92641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>1435</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2003,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628626</v>
+        <v>628590</v>
       </c>
       <c r="R15" t="n">
-        <v>6918669</v>
+        <v>6918692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,42 +2070,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127776730</v>
+        <v>127777999</v>
       </c>
       <c r="B16" t="n">
-        <v>92641</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1435</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2109,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628590</v>
+        <v>628284</v>
       </c>
       <c r="R16" t="n">
-        <v>6918692</v>
+        <v>6918798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,6 +2146,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,38 +2177,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127777999</v>
+        <v>127778755</v>
       </c>
       <c r="B17" t="n">
-        <v>57669</v>
+        <v>98504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2211,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628284</v>
+        <v>628626</v>
       </c>
       <c r="R17" t="n">
-        <v>6918798</v>
+        <v>6918669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,11 +2252,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2881,45 +2881,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127776370</v>
+        <v>127777664</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628595</v>
+        <v>628294</v>
       </c>
       <c r="R24" t="n">
-        <v>6918652</v>
+        <v>6918677</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,6 +2957,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2978,10 +2988,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776177</v>
+        <v>127776370</v>
       </c>
       <c r="B25" t="n">
-        <v>98387</v>
+        <v>98504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,28 +2999,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3053,11 +3059,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3084,37 +3085,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127775258</v>
+        <v>127776177</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3123,10 +3124,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628620</v>
+        <v>628595</v>
       </c>
       <c r="R26" t="n">
-        <v>6918640</v>
+        <v>6918652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3159,6 +3160,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3185,38 +3191,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127777664</v>
+        <v>127775258</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3225,10 +3230,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628294</v>
+        <v>628620</v>
       </c>
       <c r="R27" t="n">
-        <v>6918677</v>
+        <v>6918640</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3261,11 +3266,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4503,45 +4503,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127774928</v>
+        <v>127774434</v>
       </c>
       <c r="B40" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628665</v>
+        <v>628697</v>
       </c>
       <c r="R40" t="n">
-        <v>6918587</v>
+        <v>6918580</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,45 +4604,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127777102</v>
+        <v>127777316</v>
       </c>
       <c r="B41" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628441</v>
+        <v>628396</v>
       </c>
       <c r="R41" t="n">
-        <v>6918705</v>
+        <v>6918706</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,7 +4705,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127778769</v>
+        <v>127774928</v>
       </c>
       <c r="B42" t="n">
         <v>91352</v>
@@ -4732,10 +4740,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628626</v>
+        <v>628665</v>
       </c>
       <c r="R42" t="n">
-        <v>6918669</v>
+        <v>6918587</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,49 +4802,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127774434</v>
+        <v>127777102</v>
       </c>
       <c r="B43" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628697</v>
+        <v>628441</v>
       </c>
       <c r="R43" t="n">
-        <v>6918580</v>
+        <v>6918705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4895,49 +4899,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127777316</v>
+        <v>127778769</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628396</v>
+        <v>628626</v>
       </c>
       <c r="R44" t="n">
-        <v>6918706</v>
+        <v>6918669</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127775358</v>
+        <v>127776693</v>
       </c>
       <c r="B47" t="n">
         <v>98470</v>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628614</v>
+        <v>628590</v>
       </c>
       <c r="R47" t="n">
-        <v>6918662</v>
+        <v>6918692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5305,7 +5305,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127777752</v>
+        <v>127775358</v>
       </c>
       <c r="B48" t="n">
         <v>98470</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5344,10 +5344,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628353</v>
+        <v>628614</v>
       </c>
       <c r="R48" t="n">
-        <v>6918711</v>
+        <v>6918662</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127774205</v>
+        <v>127777752</v>
       </c>
       <c r="B49" t="n">
         <v>98470</v>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628710</v>
+        <v>628353</v>
       </c>
       <c r="R49" t="n">
-        <v>6918574</v>
+        <v>6918711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,11 +5481,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5512,7 +5507,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127776693</v>
+        <v>127774205</v>
       </c>
       <c r="B50" t="n">
         <v>98470</v>
@@ -5542,7 +5537,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5551,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628590</v>
+        <v>628710</v>
       </c>
       <c r="R50" t="n">
-        <v>6918692</v>
+        <v>6918574</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,6 +5582,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -772,48 +772,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775382</v>
+        <v>127775156</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628614</v>
+        <v>628642</v>
       </c>
       <c r="R3" t="n">
-        <v>6918662</v>
+        <v>6918602</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778500</v>
+        <v>127778961</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628416</v>
+        <v>628684</v>
       </c>
       <c r="R4" t="n">
-        <v>6918738</v>
+        <v>6918685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127778961</v>
+        <v>127778500</v>
       </c>
       <c r="B5" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628684</v>
+        <v>628416</v>
       </c>
       <c r="R5" t="n">
-        <v>6918685</v>
+        <v>6918738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,52 +1071,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775156</v>
+        <v>127775382</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628642</v>
+        <v>628614</v>
       </c>
       <c r="R6" t="n">
-        <v>6918602</v>
+        <v>6918662</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2881,50 +2881,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127777664</v>
+        <v>127776370</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628294</v>
+        <v>628595</v>
       </c>
       <c r="R24" t="n">
-        <v>6918677</v>
+        <v>6918652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2988,10 +2978,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776370</v>
+        <v>127776177</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>98387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2999,24 +2989,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3059,6 +3053,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3085,37 +3084,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127776177</v>
+        <v>127775258</v>
       </c>
       <c r="B26" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3124,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628595</v>
+        <v>628620</v>
       </c>
       <c r="R26" t="n">
-        <v>6918652</v>
+        <v>6918640</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3160,11 +3159,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3191,37 +3185,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127775258</v>
+        <v>127777664</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3230,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628620</v>
+        <v>628294</v>
       </c>
       <c r="R27" t="n">
-        <v>6918640</v>
+        <v>6918677</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,6 +3261,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5204,7 +5204,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127776693</v>
+        <v>127775358</v>
       </c>
       <c r="B47" t="n">
         <v>98470</v>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628590</v>
+        <v>628614</v>
       </c>
       <c r="R47" t="n">
-        <v>6918692</v>
+        <v>6918662</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5305,7 +5305,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127775358</v>
+        <v>127777752</v>
       </c>
       <c r="B48" t="n">
         <v>98470</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5344,10 +5344,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628614</v>
+        <v>628353</v>
       </c>
       <c r="R48" t="n">
-        <v>6918662</v>
+        <v>6918711</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5406,7 +5406,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127777752</v>
+        <v>127774205</v>
       </c>
       <c r="B49" t="n">
         <v>98470</v>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628353</v>
+        <v>628710</v>
       </c>
       <c r="R49" t="n">
-        <v>6918711</v>
+        <v>6918574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,6 +5481,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5507,7 +5512,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127774205</v>
+        <v>127776693</v>
       </c>
       <c r="B50" t="n">
         <v>98470</v>
@@ -5537,7 +5542,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5546,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628710</v>
+        <v>628590</v>
       </c>
       <c r="R50" t="n">
-        <v>6918574</v>
+        <v>6918692</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5582,11 +5587,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -772,52 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775156</v>
+        <v>127775382</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628642</v>
+        <v>628614</v>
       </c>
       <c r="R3" t="n">
-        <v>6918602</v>
+        <v>6918662</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778961</v>
+        <v>127778500</v>
       </c>
       <c r="B4" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628684</v>
+        <v>628416</v>
       </c>
       <c r="R4" t="n">
-        <v>6918685</v>
+        <v>6918738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127778500</v>
+        <v>127778961</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628416</v>
+        <v>628684</v>
       </c>
       <c r="R5" t="n">
-        <v>6918738</v>
+        <v>6918685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,48 +1067,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775382</v>
+        <v>127775156</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628614</v>
+        <v>628642</v>
       </c>
       <c r="R6" t="n">
-        <v>6918662</v>
+        <v>6918602</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1463,49 +1463,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127775915</v>
+        <v>127778586</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628612</v>
+        <v>628451</v>
       </c>
       <c r="R10" t="n">
-        <v>6918686</v>
+        <v>6918725</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,7 +1560,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127774280</v>
+        <v>127775915</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1594,7 +1590,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1603,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628702</v>
+        <v>628612</v>
       </c>
       <c r="R11" t="n">
-        <v>6918572</v>
+        <v>6918686</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1661,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127777577</v>
+        <v>127774280</v>
       </c>
       <c r="B12" t="n">
         <v>98470</v>
@@ -1695,7 +1691,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1704,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628305</v>
+        <v>628702</v>
       </c>
       <c r="R12" t="n">
-        <v>6918693</v>
+        <v>6918572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127775315</v>
+        <v>127777577</v>
       </c>
       <c r="B13" t="n">
         <v>98470</v>
@@ -1796,7 +1792,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1805,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628627</v>
+        <v>628305</v>
       </c>
       <c r="R13" t="n">
-        <v>6918612</v>
+        <v>6918693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,45 +1863,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127778586</v>
+        <v>127775315</v>
       </c>
       <c r="B14" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628451</v>
+        <v>628627</v>
       </c>
       <c r="R14" t="n">
-        <v>6918725</v>
+        <v>6918612</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -4996,42 +4996,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127778954</v>
+        <v>127775358</v>
       </c>
       <c r="B45" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5040,10 +5035,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628675</v>
+        <v>628614</v>
       </c>
       <c r="R45" t="n">
-        <v>6918656</v>
+        <v>6918662</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5102,38 +5097,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127774067</v>
+        <v>127777752</v>
       </c>
       <c r="B46" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5142,10 +5136,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628716</v>
+        <v>628353</v>
       </c>
       <c r="R46" t="n">
-        <v>6918568</v>
+        <v>6918711</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5204,7 +5198,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127775358</v>
+        <v>127774205</v>
       </c>
       <c r="B47" t="n">
         <v>98470</v>
@@ -5234,7 +5228,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5243,10 +5237,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628614</v>
+        <v>628710</v>
       </c>
       <c r="R47" t="n">
-        <v>6918662</v>
+        <v>6918574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5279,6 +5273,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5305,7 +5304,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127777752</v>
+        <v>127775875</v>
       </c>
       <c r="B48" t="n">
         <v>98470</v>
@@ -5335,7 +5334,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5344,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628353</v>
+        <v>628595</v>
       </c>
       <c r="R48" t="n">
-        <v>6918711</v>
+        <v>6918652</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5380,6 +5379,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5406,37 +5410,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127774205</v>
+        <v>127778954</v>
       </c>
       <c r="B49" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5445,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628710</v>
+        <v>628675</v>
       </c>
       <c r="R49" t="n">
-        <v>6918574</v>
+        <v>6918656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,11 +5490,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5512,37 +5516,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127776693</v>
+        <v>127774067</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5551,10 +5556,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628590</v>
+        <v>628716</v>
       </c>
       <c r="R50" t="n">
-        <v>6918692</v>
+        <v>6918568</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5613,7 +5618,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127775875</v>
+        <v>127776693</v>
       </c>
       <c r="B51" t="n">
         <v>98470</v>
@@ -5643,7 +5648,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5652,10 +5657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628595</v>
+        <v>628590</v>
       </c>
       <c r="R51" t="n">
-        <v>6918652</v>
+        <v>6918692</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5688,11 +5693,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -2881,45 +2881,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127776370</v>
+        <v>127777664</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628595</v>
+        <v>628294</v>
       </c>
       <c r="R24" t="n">
-        <v>6918652</v>
+        <v>6918677</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,6 +2957,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2978,10 +2988,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776177</v>
+        <v>127776370</v>
       </c>
       <c r="B25" t="n">
-        <v>98387</v>
+        <v>98504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,28 +2999,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3053,11 +3059,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3084,37 +3085,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127775258</v>
+        <v>127776177</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3123,10 +3124,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628620</v>
+        <v>628595</v>
       </c>
       <c r="R26" t="n">
-        <v>6918640</v>
+        <v>6918652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3159,6 +3160,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3185,38 +3191,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127777664</v>
+        <v>127775258</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3225,10 +3230,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628294</v>
+        <v>628620</v>
       </c>
       <c r="R27" t="n">
-        <v>6918677</v>
+        <v>6918640</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3261,11 +3266,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -772,48 +772,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775382</v>
+        <v>127775156</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628614</v>
+        <v>628642</v>
       </c>
       <c r="R3" t="n">
-        <v>6918662</v>
+        <v>6918602</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778500</v>
+        <v>127778961</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628416</v>
+        <v>628684</v>
       </c>
       <c r="R4" t="n">
-        <v>6918738</v>
+        <v>6918685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127778961</v>
+        <v>127778500</v>
       </c>
       <c r="B5" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628684</v>
+        <v>628416</v>
       </c>
       <c r="R5" t="n">
-        <v>6918685</v>
+        <v>6918738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,52 +1071,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775156</v>
+        <v>127775382</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628642</v>
+        <v>628614</v>
       </c>
       <c r="R6" t="n">
-        <v>6918602</v>
+        <v>6918662</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1463,45 +1463,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778586</v>
+        <v>127775915</v>
       </c>
       <c r="B10" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628451</v>
+        <v>628612</v>
       </c>
       <c r="R10" t="n">
-        <v>6918725</v>
+        <v>6918686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,7 +1564,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127775915</v>
+        <v>127774280</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1590,7 +1594,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1599,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628612</v>
+        <v>628702</v>
       </c>
       <c r="R11" t="n">
-        <v>6918686</v>
+        <v>6918572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,7 +1665,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127774280</v>
+        <v>127777577</v>
       </c>
       <c r="B12" t="n">
         <v>98470</v>
@@ -1691,7 +1695,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1700,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628702</v>
+        <v>628305</v>
       </c>
       <c r="R12" t="n">
-        <v>6918572</v>
+        <v>6918693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1766,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127777577</v>
+        <v>127775315</v>
       </c>
       <c r="B13" t="n">
         <v>98470</v>
@@ -1792,7 +1796,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1801,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628305</v>
+        <v>628627</v>
       </c>
       <c r="R13" t="n">
-        <v>6918693</v>
+        <v>6918612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,49 +1867,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127775315</v>
+        <v>127778586</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628627</v>
+        <v>628451</v>
       </c>
       <c r="R14" t="n">
-        <v>6918612</v>
+        <v>6918725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -772,52 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775156</v>
+        <v>127775382</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628642</v>
+        <v>628614</v>
       </c>
       <c r="R3" t="n">
-        <v>6918602</v>
+        <v>6918662</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778961</v>
+        <v>127778500</v>
       </c>
       <c r="B4" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628684</v>
+        <v>628416</v>
       </c>
       <c r="R4" t="n">
-        <v>6918685</v>
+        <v>6918738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127778500</v>
+        <v>127778961</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628416</v>
+        <v>628684</v>
       </c>
       <c r="R5" t="n">
-        <v>6918738</v>
+        <v>6918685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,48 +1067,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775382</v>
+        <v>127775156</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628614</v>
+        <v>628642</v>
       </c>
       <c r="R6" t="n">
-        <v>6918662</v>
+        <v>6918602</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,49 +1265,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778802</v>
+        <v>127774181</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>91317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628634</v>
+        <v>628716</v>
       </c>
       <c r="R8" t="n">
-        <v>6918656</v>
+        <v>6918568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,45 +1362,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774181</v>
+        <v>127778802</v>
       </c>
       <c r="B9" t="n">
-        <v>91317</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628716</v>
+        <v>628634</v>
       </c>
       <c r="R9" t="n">
-        <v>6918568</v>
+        <v>6918656</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2881,50 +2881,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127777664</v>
+        <v>127776370</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628294</v>
+        <v>628595</v>
       </c>
       <c r="R24" t="n">
-        <v>6918677</v>
+        <v>6918652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2988,10 +2978,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776370</v>
+        <v>127776177</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>98387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2999,24 +2989,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3059,6 +3053,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3085,37 +3084,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127776177</v>
+        <v>127775258</v>
       </c>
       <c r="B26" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3124,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628595</v>
+        <v>628620</v>
       </c>
       <c r="R26" t="n">
-        <v>6918652</v>
+        <v>6918640</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3160,11 +3159,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3191,37 +3185,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127775258</v>
+        <v>127777664</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3230,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628620</v>
+        <v>628294</v>
       </c>
       <c r="R27" t="n">
-        <v>6918640</v>
+        <v>6918677</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,6 +3261,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127774666</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127775382</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127778500</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,48 +970,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127778961</v>
+        <v>127775156</v>
       </c>
       <c r="B5" t="n">
-        <v>97347</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628684</v>
+        <v>628642</v>
       </c>
       <c r="R5" t="n">
-        <v>6918685</v>
+        <v>6918602</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,52 +1071,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775156</v>
+        <v>127778961</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>97355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628642</v>
+        <v>628684</v>
       </c>
       <c r="R6" t="n">
-        <v>6918602</v>
+        <v>6918685</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>127775456</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,45 +1265,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127774181</v>
+        <v>127778802</v>
       </c>
       <c r="B8" t="n">
-        <v>91317</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628716</v>
+        <v>628634</v>
       </c>
       <c r="R8" t="n">
-        <v>6918568</v>
+        <v>6918656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,49 +1366,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127778802</v>
+        <v>127774181</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>91325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628634</v>
+        <v>628716</v>
       </c>
       <c r="R9" t="n">
-        <v>6918656</v>
+        <v>6918568</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,49 +1463,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127775915</v>
+        <v>127778586</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>98395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628612</v>
+        <v>628451</v>
       </c>
       <c r="R10" t="n">
-        <v>6918686</v>
+        <v>6918725</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1560,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127774280</v>
+        <v>127775915</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,7 +1590,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1603,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628702</v>
+        <v>628612</v>
       </c>
       <c r="R11" t="n">
-        <v>6918572</v>
+        <v>6918686</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127777577</v>
+        <v>127774280</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,7 +1691,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1704,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628305</v>
+        <v>628702</v>
       </c>
       <c r="R12" t="n">
-        <v>6918693</v>
+        <v>6918572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127775315</v>
+        <v>127777577</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,7 +1792,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1805,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628627</v>
+        <v>628305</v>
       </c>
       <c r="R13" t="n">
-        <v>6918612</v>
+        <v>6918693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,45 +1863,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127778586</v>
+        <v>127775315</v>
       </c>
       <c r="B14" t="n">
-        <v>98387</v>
+        <v>98478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628451</v>
+        <v>628627</v>
       </c>
       <c r="R14" t="n">
-        <v>6918725</v>
+        <v>6918612</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>127776730</v>
       </c>
       <c r="B15" t="n">
-        <v>92641</v>
+        <v>92649</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,38 +2070,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127777999</v>
+        <v>127778755</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>98512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2110,10 +2109,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628284</v>
+        <v>628626</v>
       </c>
       <c r="R16" t="n">
-        <v>6918798</v>
+        <v>6918669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,11 +2145,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2177,37 +2171,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127778755</v>
+        <v>127777999</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>57670</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2216,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628626</v>
+        <v>628284</v>
       </c>
       <c r="R17" t="n">
-        <v>6918669</v>
+        <v>6918798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,6 +2247,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2281,7 +2281,7 @@
         <v>127775800</v>
       </c>
       <c r="B18" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>127774703</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127777111</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>127775985</v>
       </c>
       <c r="B21" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>127777244</v>
       </c>
       <c r="B22" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>127778761</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2881,45 +2881,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127776370</v>
+        <v>127775258</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628595</v>
+        <v>628620</v>
       </c>
       <c r="R24" t="n">
-        <v>6918652</v>
+        <v>6918640</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2978,10 +2982,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776177</v>
+        <v>127776370</v>
       </c>
       <c r="B25" t="n">
-        <v>98387</v>
+        <v>98512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,28 +2993,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3053,11 +3053,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3084,37 +3079,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127775258</v>
+        <v>127776177</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98395</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3123,10 +3118,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628620</v>
+        <v>628595</v>
       </c>
       <c r="R26" t="n">
-        <v>6918640</v>
+        <v>6918652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3159,6 +3154,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,7 +3188,7 @@
         <v>127777664</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>127774870</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>127776178</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>127777628</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>127776816</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127777928</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127778213</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>127775104</v>
       </c>
       <c r="B34" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>127778222</v>
       </c>
       <c r="B35" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4097,38 +4097,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127776955</v>
+        <v>127778286</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>44</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4137,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628471</v>
+        <v>628333</v>
       </c>
       <c r="R36" t="n">
-        <v>6918667</v>
+        <v>6918773</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,11 +4172,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4204,37 +4198,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127778286</v>
+        <v>127776955</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>44</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4243,10 +4238,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628333</v>
+        <v>628471</v>
       </c>
       <c r="R37" t="n">
-        <v>6918773</v>
+        <v>6918667</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,6 +4274,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,7 +4308,7 @@
         <v>127776189</v>
       </c>
       <c r="B38" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>127777903</v>
       </c>
       <c r="B39" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,49 +4503,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127774434</v>
+        <v>127778769</v>
       </c>
       <c r="B40" t="n">
-        <v>98470</v>
+        <v>91360</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628697</v>
+        <v>628626</v>
       </c>
       <c r="R40" t="n">
-        <v>6918580</v>
+        <v>6918669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4604,49 +4600,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127777316</v>
+        <v>127774928</v>
       </c>
       <c r="B41" t="n">
-        <v>98470</v>
+        <v>91360</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628396</v>
+        <v>628665</v>
       </c>
       <c r="R41" t="n">
-        <v>6918706</v>
+        <v>6918587</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4705,10 +4697,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127774928</v>
+        <v>127777102</v>
       </c>
       <c r="B42" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628665</v>
+        <v>628441</v>
       </c>
       <c r="R42" t="n">
-        <v>6918587</v>
+        <v>6918705</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4802,45 +4794,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127777102</v>
+        <v>127774434</v>
       </c>
       <c r="B43" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628441</v>
+        <v>628697</v>
       </c>
       <c r="R43" t="n">
-        <v>6918705</v>
+        <v>6918580</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4899,45 +4895,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127778769</v>
+        <v>127777316</v>
       </c>
       <c r="B44" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628626</v>
+        <v>628396</v>
       </c>
       <c r="R44" t="n">
-        <v>6918669</v>
+        <v>6918706</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,37 +4996,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127775358</v>
+        <v>127774067</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>57833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5035,10 +5036,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628614</v>
+        <v>628716</v>
       </c>
       <c r="R45" t="n">
-        <v>6918662</v>
+        <v>6918568</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5097,37 +5098,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127777752</v>
+        <v>127778954</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>92650</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5136,10 +5142,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628353</v>
+        <v>628675</v>
       </c>
       <c r="R46" t="n">
-        <v>6918711</v>
+        <v>6918656</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5198,10 +5204,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127774205</v>
+        <v>127775358</v>
       </c>
       <c r="B47" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5228,7 +5234,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5237,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628710</v>
+        <v>628614</v>
       </c>
       <c r="R47" t="n">
-        <v>6918574</v>
+        <v>6918662</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5273,11 +5279,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5304,10 +5305,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127775875</v>
+        <v>127777752</v>
       </c>
       <c r="B48" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,7 +5335,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5343,10 +5344,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628595</v>
+        <v>628353</v>
       </c>
       <c r="R48" t="n">
-        <v>6918652</v>
+        <v>6918711</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5379,11 +5380,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5410,42 +5406,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127778954</v>
+        <v>127774205</v>
       </c>
       <c r="B49" t="n">
-        <v>92642</v>
+        <v>98478</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5454,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628675</v>
+        <v>628710</v>
       </c>
       <c r="R49" t="n">
-        <v>6918656</v>
+        <v>6918574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5490,6 +5481,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5516,38 +5512,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127774067</v>
+        <v>127776693</v>
       </c>
       <c r="B50" t="n">
-        <v>57832</v>
+        <v>98478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5556,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628716</v>
+        <v>628590</v>
       </c>
       <c r="R50" t="n">
-        <v>6918568</v>
+        <v>6918692</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5618,10 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127776693</v>
+        <v>127775875</v>
       </c>
       <c r="B51" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5648,7 +5643,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5657,10 +5652,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628590</v>
+        <v>628595</v>
       </c>
       <c r="R51" t="n">
-        <v>6918692</v>
+        <v>6918652</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5693,6 +5688,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5722,7 +5722,7 @@
         <v>127774353</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>127834723</v>
       </c>
       <c r="B53" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>127836030</v>
       </c>
       <c r="B54" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>127836087</v>
       </c>
       <c r="B55" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6111,48 +6111,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127833952</v>
+        <v>127834972</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>98512</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupmyran, Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628647</v>
+        <v>628267</v>
       </c>
       <c r="R56" t="n">
-        <v>6918692</v>
+        <v>6918732</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6193,7 +6190,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6212,45 +6208,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127834972</v>
+        <v>127833952</v>
       </c>
       <c r="B57" t="n">
-        <v>98504</v>
+        <v>79032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Djupmyran, Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628267</v>
+        <v>628647</v>
       </c>
       <c r="R57" t="n">
-        <v>6918732</v>
+        <v>6918692</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6291,6 +6290,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -2070,37 +2070,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127778755</v>
+        <v>127777999</v>
       </c>
       <c r="B16" t="n">
-        <v>98512</v>
+        <v>57670</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2109,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628626</v>
+        <v>628284</v>
       </c>
       <c r="R16" t="n">
-        <v>6918669</v>
+        <v>6918798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,6 +2146,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,38 +2177,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127777999</v>
+        <v>127778755</v>
       </c>
       <c r="B17" t="n">
-        <v>57670</v>
+        <v>98512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2211,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628284</v>
+        <v>628626</v>
       </c>
       <c r="R17" t="n">
-        <v>6918798</v>
+        <v>6918669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,11 +2252,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2881,49 +2881,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127775258</v>
+        <v>127776370</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>98512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628620</v>
+        <v>628595</v>
       </c>
       <c r="R24" t="n">
-        <v>6918640</v>
+        <v>6918652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2982,10 +2978,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776370</v>
+        <v>127776177</v>
       </c>
       <c r="B25" t="n">
-        <v>98512</v>
+        <v>98395</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2993,24 +2989,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
@@ -3053,6 +3053,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3079,37 +3084,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127776177</v>
+        <v>127775258</v>
       </c>
       <c r="B26" t="n">
-        <v>98395</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3118,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628595</v>
+        <v>628620</v>
       </c>
       <c r="R26" t="n">
-        <v>6918652</v>
+        <v>6918640</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3154,11 +3159,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4097,37 +4097,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127778286</v>
+        <v>127776955</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>44</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4136,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628333</v>
+        <v>628471</v>
       </c>
       <c r="R36" t="n">
-        <v>6918773</v>
+        <v>6918667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,6 +4173,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,38 +4204,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127776955</v>
+        <v>127778286</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>98478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>44</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4238,10 +4243,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628471</v>
+        <v>628333</v>
       </c>
       <c r="R37" t="n">
-        <v>6918667</v>
+        <v>6918773</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,11 +4279,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127774666</v>
       </c>
       <c r="B2" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,48 +772,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775382</v>
+        <v>127775156</v>
       </c>
       <c r="B3" t="n">
-        <v>98512</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628614</v>
+        <v>628642</v>
       </c>
       <c r="R3" t="n">
-        <v>6918662</v>
+        <v>6918602</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778500</v>
+        <v>127778961</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>97448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628416</v>
+        <v>628684</v>
       </c>
       <c r="R4" t="n">
-        <v>6918738</v>
+        <v>6918685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,52 +970,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775156</v>
+        <v>127775382</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628642</v>
+        <v>628614</v>
       </c>
       <c r="R5" t="n">
-        <v>6918602</v>
+        <v>6918662</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,45 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778961</v>
+        <v>127778500</v>
       </c>
       <c r="B6" t="n">
-        <v>97355</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628684</v>
+        <v>628416</v>
       </c>
       <c r="R6" t="n">
-        <v>6918685</v>
+        <v>6918738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
         <v>127775456</v>
       </c>
       <c r="B7" t="n">
-        <v>98512</v>
+        <v>98605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127778802</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>127774181</v>
       </c>
       <c r="B9" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,45 +1463,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127778586</v>
+        <v>127774280</v>
       </c>
       <c r="B10" t="n">
-        <v>98395</v>
+        <v>98571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628451</v>
+        <v>628702</v>
       </c>
       <c r="R10" t="n">
-        <v>6918725</v>
+        <v>6918572</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1567,7 @@
         <v>127775915</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127774280</v>
+        <v>127777577</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,7 +1695,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1700,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628702</v>
+        <v>628305</v>
       </c>
       <c r="R12" t="n">
-        <v>6918572</v>
+        <v>6918693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,49 +1766,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127777577</v>
+        <v>127778586</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628305</v>
+        <v>628451</v>
       </c>
       <c r="R13" t="n">
-        <v>6918693</v>
+        <v>6918725</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,7 +1866,7 @@
         <v>127775315</v>
       </c>
       <c r="B14" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,42 +1964,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127776730</v>
+        <v>127778755</v>
       </c>
       <c r="B15" t="n">
-        <v>92649</v>
+        <v>98605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1435</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2008,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628590</v>
+        <v>628626</v>
       </c>
       <c r="R15" t="n">
-        <v>6918692</v>
+        <v>6918669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,38 +2065,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127777999</v>
+        <v>127776730</v>
       </c>
       <c r="B16" t="n">
-        <v>57670</v>
+        <v>92741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1435</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2110,10 +2109,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628284</v>
+        <v>628590</v>
       </c>
       <c r="R16" t="n">
-        <v>6918798</v>
+        <v>6918692</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,11 +2145,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2177,37 +2171,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127778755</v>
+        <v>127777999</v>
       </c>
       <c r="B17" t="n">
-        <v>98512</v>
+        <v>57682</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2216,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628626</v>
+        <v>628284</v>
       </c>
       <c r="R17" t="n">
-        <v>6918669</v>
+        <v>6918798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,6 +2247,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2281,7 +2281,7 @@
         <v>127775800</v>
       </c>
       <c r="B18" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>127774703</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127777111</v>
       </c>
       <c r="B20" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,38 +2577,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127775985</v>
+        <v>127777244</v>
       </c>
       <c r="B21" t="n">
-        <v>57833</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2617,10 +2616,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628607</v>
+        <v>628416</v>
       </c>
       <c r="R21" t="n">
-        <v>6918700</v>
+        <v>6918688</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,10 +2678,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127777244</v>
+        <v>127778761</v>
       </c>
       <c r="B22" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2709,7 +2708,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2718,10 +2717,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628416</v>
+        <v>628633</v>
       </c>
       <c r="R22" t="n">
-        <v>6918688</v>
+        <v>6918629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,37 +2779,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127778761</v>
+        <v>127775985</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>57845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628633</v>
+        <v>628607</v>
       </c>
       <c r="R23" t="n">
-        <v>6918629</v>
+        <v>6918700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2884,7 +2884,7 @@
         <v>127776370</v>
       </c>
       <c r="B24" t="n">
-        <v>98512</v>
+        <v>98605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>127776177</v>
       </c>
       <c r="B25" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>127775258</v>
       </c>
       <c r="B26" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>127777664</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127774870</v>
+        <v>127777628</v>
       </c>
       <c r="B28" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628653</v>
+        <v>628304</v>
       </c>
       <c r="R28" t="n">
-        <v>6918622</v>
+        <v>6918675</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127776178</v>
+        <v>127774870</v>
       </c>
       <c r="B29" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628598</v>
+        <v>628653</v>
       </c>
       <c r="R29" t="n">
-        <v>6918670</v>
+        <v>6918622</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127777628</v>
+        <v>127776178</v>
       </c>
       <c r="B30" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628304</v>
+        <v>628598</v>
       </c>
       <c r="R30" t="n">
-        <v>6918675</v>
+        <v>6918670</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
         <v>127776816</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127777928</v>
       </c>
       <c r="B32" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127778213</v>
       </c>
       <c r="B33" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127775104</v>
+        <v>127778222</v>
       </c>
       <c r="B34" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628633</v>
+        <v>628315</v>
       </c>
       <c r="R34" t="n">
-        <v>6918629</v>
+        <v>6918803</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127778222</v>
+        <v>127775104</v>
       </c>
       <c r="B35" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628315</v>
+        <v>628633</v>
       </c>
       <c r="R35" t="n">
-        <v>6918803</v>
+        <v>6918629</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,38 +4097,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127776955</v>
+        <v>127778286</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>44</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4137,10 +4136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628471</v>
+        <v>628333</v>
       </c>
       <c r="R36" t="n">
-        <v>6918667</v>
+        <v>6918773</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,11 +4172,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4204,37 +4198,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127778286</v>
+        <v>127776955</v>
       </c>
       <c r="B37" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>44</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4243,10 +4238,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628333</v>
+        <v>628471</v>
       </c>
       <c r="R37" t="n">
-        <v>6918773</v>
+        <v>6918667</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,6 +4274,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4308,7 +4308,7 @@
         <v>127776189</v>
       </c>
       <c r="B38" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>127777903</v>
       </c>
       <c r="B39" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>127778769</v>
       </c>
       <c r="B40" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>127774928</v>
       </c>
       <c r="B41" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127777102</v>
       </c>
       <c r="B42" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>127774434</v>
       </c>
       <c r="B43" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127777316</v>
       </c>
       <c r="B44" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4996,38 +4996,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127774067</v>
+        <v>127778954</v>
       </c>
       <c r="B45" t="n">
-        <v>57833</v>
+        <v>92742</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5036,10 +5040,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628716</v>
+        <v>628675</v>
       </c>
       <c r="R45" t="n">
-        <v>6918568</v>
+        <v>6918656</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,42 +5102,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127778954</v>
+        <v>127776693</v>
       </c>
       <c r="B46" t="n">
-        <v>92650</v>
+        <v>98571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5142,10 +5141,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628675</v>
+        <v>628590</v>
       </c>
       <c r="R46" t="n">
-        <v>6918656</v>
+        <v>6918692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5207,7 +5206,7 @@
         <v>127775358</v>
       </c>
       <c r="B47" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,10 +5304,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127777752</v>
+        <v>127774205</v>
       </c>
       <c r="B48" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5335,7 +5334,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5344,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628353</v>
+        <v>628710</v>
       </c>
       <c r="R48" t="n">
-        <v>6918711</v>
+        <v>6918574</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5380,6 +5379,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5406,10 +5410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127774205</v>
+        <v>127777752</v>
       </c>
       <c r="B49" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5436,7 +5440,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5445,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628710</v>
+        <v>628353</v>
       </c>
       <c r="R49" t="n">
-        <v>6918574</v>
+        <v>6918711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,11 +5485,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5512,10 +5511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127776693</v>
+        <v>127775875</v>
       </c>
       <c r="B50" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5542,7 +5541,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5551,10 +5550,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628590</v>
+        <v>628595</v>
       </c>
       <c r="R50" t="n">
-        <v>6918692</v>
+        <v>6918652</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,6 +5586,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5613,37 +5617,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127775875</v>
+        <v>127774067</v>
       </c>
       <c r="B51" t="n">
-        <v>98478</v>
+        <v>57845</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5652,10 +5657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628595</v>
+        <v>628716</v>
       </c>
       <c r="R51" t="n">
-        <v>6918652</v>
+        <v>6918568</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5688,11 +5693,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5722,7 +5722,7 @@
         <v>127774353</v>
       </c>
       <c r="B52" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>127834723</v>
       </c>
       <c r="B53" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>127836030</v>
       </c>
       <c r="B54" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>127836087</v>
       </c>
       <c r="B55" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6111,45 +6111,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127834972</v>
+        <v>127833952</v>
       </c>
       <c r="B56" t="n">
-        <v>98512</v>
+        <v>79083</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupmyran, Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628267</v>
+        <v>628647</v>
       </c>
       <c r="R56" t="n">
-        <v>6918732</v>
+        <v>6918692</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6190,6 +6193,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6208,48 +6212,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127833952</v>
+        <v>127834972</v>
       </c>
       <c r="B57" t="n">
-        <v>79032</v>
+        <v>98605</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Djupmyran, Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628647</v>
+        <v>628267</v>
       </c>
       <c r="R57" t="n">
-        <v>6918692</v>
+        <v>6918732</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6290,7 +6291,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127774666</v>
+        <v>127775382</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>98605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628697</v>
+        <v>628614</v>
       </c>
       <c r="R2" t="n">
-        <v>6918580</v>
+        <v>6918662</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775156</v>
+        <v>127778500</v>
       </c>
       <c r="B3" t="n">
         <v>98571</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628642</v>
+        <v>628416</v>
       </c>
       <c r="R3" t="n">
-        <v>6918602</v>
+        <v>6918738</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,48 +873,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127778961</v>
+        <v>127775156</v>
       </c>
       <c r="B4" t="n">
-        <v>97448</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628684</v>
+        <v>628642</v>
       </c>
       <c r="R4" t="n">
-        <v>6918685</v>
+        <v>6918602</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775382</v>
+        <v>127778961</v>
       </c>
       <c r="B5" t="n">
-        <v>98605</v>
+        <v>97448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628614</v>
+        <v>628684</v>
       </c>
       <c r="R5" t="n">
-        <v>6918662</v>
+        <v>6918685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,49 +1071,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127778500</v>
+        <v>127774666</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>91452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628416</v>
+        <v>628697</v>
       </c>
       <c r="R6" t="n">
-        <v>6918738</v>
+        <v>6918580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,49 +1265,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127778802</v>
+        <v>127774181</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>91417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628634</v>
+        <v>628716</v>
       </c>
       <c r="R8" t="n">
-        <v>6918656</v>
+        <v>6918568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,45 +1362,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774181</v>
+        <v>127778802</v>
       </c>
       <c r="B9" t="n">
-        <v>91417</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628716</v>
+        <v>628634</v>
       </c>
       <c r="R9" t="n">
-        <v>6918568</v>
+        <v>6918656</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,49 +1463,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127774280</v>
+        <v>127778586</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628702</v>
+        <v>628451</v>
       </c>
       <c r="R10" t="n">
-        <v>6918572</v>
+        <v>6918725</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,7 +1560,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127775915</v>
+        <v>127774280</v>
       </c>
       <c r="B11" t="n">
         <v>98571</v>
@@ -1594,7 +1590,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1603,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628612</v>
+        <v>628702</v>
       </c>
       <c r="R11" t="n">
-        <v>6918686</v>
+        <v>6918572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1661,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127777577</v>
+        <v>127775915</v>
       </c>
       <c r="B12" t="n">
         <v>98571</v>
@@ -1695,7 +1691,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1704,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628305</v>
+        <v>628612</v>
       </c>
       <c r="R12" t="n">
-        <v>6918693</v>
+        <v>6918686</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,45 +1762,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127778586</v>
+        <v>127777577</v>
       </c>
       <c r="B13" t="n">
-        <v>98488</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628451</v>
+        <v>628305</v>
       </c>
       <c r="R13" t="n">
-        <v>6918725</v>
+        <v>6918693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,42 +2065,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127776730</v>
+        <v>127777999</v>
       </c>
       <c r="B16" t="n">
-        <v>92741</v>
+        <v>57682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1435</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2109,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628590</v>
+        <v>628284</v>
       </c>
       <c r="R16" t="n">
-        <v>6918692</v>
+        <v>6918798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,6 +2141,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,38 +2172,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127777999</v>
+        <v>127776730</v>
       </c>
       <c r="B17" t="n">
-        <v>57682</v>
+        <v>92741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1435</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2211,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628284</v>
+        <v>628590</v>
       </c>
       <c r="R17" t="n">
-        <v>6918798</v>
+        <v>6918692</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,11 +2252,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosök på liggande död gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2577,37 +2577,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127777244</v>
+        <v>127775985</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>28</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2616,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628416</v>
+        <v>628607</v>
       </c>
       <c r="R21" t="n">
-        <v>6918688</v>
+        <v>6918700</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,7 +2679,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127778761</v>
+        <v>127777244</v>
       </c>
       <c r="B22" t="n">
         <v>98571</v>
@@ -2708,7 +2709,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2717,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628633</v>
+        <v>628416</v>
       </c>
       <c r="R22" t="n">
-        <v>6918629</v>
+        <v>6918688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2779,38 +2780,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127775985</v>
+        <v>127778761</v>
       </c>
       <c r="B23" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628607</v>
+        <v>628633</v>
       </c>
       <c r="R23" t="n">
-        <v>6918700</v>
+        <v>6918629</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2881,45 +2881,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127776370</v>
+        <v>127777664</v>
       </c>
       <c r="B24" t="n">
-        <v>98605</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628595</v>
+        <v>628294</v>
       </c>
       <c r="R24" t="n">
-        <v>6918652</v>
+        <v>6918677</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,6 +2957,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2978,37 +2988,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127776177</v>
+        <v>127775318</v>
       </c>
       <c r="B25" t="n">
-        <v>98488</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3017,10 +3027,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628595</v>
+        <v>628620</v>
       </c>
       <c r="R25" t="n">
-        <v>6918652</v>
+        <v>6918640</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3053,11 +3063,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3084,37 +3089,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127775258</v>
+        <v>127776177</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3123,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628620</v>
+        <v>628595</v>
       </c>
       <c r="R26" t="n">
-        <v>6918640</v>
+        <v>6918652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3159,6 +3164,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Förekommer inom våt området</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3185,50 +3195,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127777664</v>
+        <v>127776370</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>98605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628294</v>
+        <v>628595</v>
       </c>
       <c r="R27" t="n">
-        <v>6918677</v>
+        <v>6918652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3261,11 +3266,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3903,7 +3903,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127778222</v>
+        <v>127775104</v>
       </c>
       <c r="B34" t="n">
         <v>91452</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628315</v>
+        <v>628633</v>
       </c>
       <c r="R34" t="n">
-        <v>6918803</v>
+        <v>6918629</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127775104</v>
+        <v>127778222</v>
       </c>
       <c r="B35" t="n">
         <v>91452</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628633</v>
+        <v>628315</v>
       </c>
       <c r="R35" t="n">
-        <v>6918629</v>
+        <v>6918803</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,37 +4097,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127778286</v>
+        <v>127776955</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>44</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4136,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628333</v>
+        <v>628471</v>
       </c>
       <c r="R36" t="n">
-        <v>6918773</v>
+        <v>6918667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,6 +4173,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4198,38 +4204,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127776955</v>
+        <v>127778286</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>44</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4238,10 +4243,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628471</v>
+        <v>628333</v>
       </c>
       <c r="R37" t="n">
-        <v>6918667</v>
+        <v>6918773</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,11 +4279,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5102,37 +5102,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127776693</v>
+        <v>127774067</v>
       </c>
       <c r="B46" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5141,10 +5142,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628590</v>
+        <v>628716</v>
       </c>
       <c r="R46" t="n">
-        <v>6918692</v>
+        <v>6918568</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5203,7 +5204,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127775358</v>
+        <v>127776693</v>
       </c>
       <c r="B47" t="n">
         <v>98571</v>
@@ -5242,10 +5243,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628614</v>
+        <v>628590</v>
       </c>
       <c r="R47" t="n">
-        <v>6918662</v>
+        <v>6918692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5304,7 +5305,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127774205</v>
+        <v>127775358</v>
       </c>
       <c r="B48" t="n">
         <v>98571</v>
@@ -5334,7 +5335,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5343,10 +5344,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628710</v>
+        <v>628614</v>
       </c>
       <c r="R48" t="n">
-        <v>6918574</v>
+        <v>6918662</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5379,11 +5380,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5410,7 +5406,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127777752</v>
+        <v>127774205</v>
       </c>
       <c r="B49" t="n">
         <v>98571</v>
@@ -5440,7 +5436,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5449,10 +5445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628353</v>
+        <v>628710</v>
       </c>
       <c r="R49" t="n">
-        <v>6918711</v>
+        <v>6918574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5485,6 +5481,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påväg att blomma</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5511,7 +5512,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127775875</v>
+        <v>127777752</v>
       </c>
       <c r="B50" t="n">
         <v>98571</v>
@@ -5541,7 +5542,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5550,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628595</v>
+        <v>628353</v>
       </c>
       <c r="R50" t="n">
-        <v>6918652</v>
+        <v>6918711</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5586,11 +5587,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5617,38 +5613,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127774067</v>
+        <v>127775875</v>
       </c>
       <c r="B51" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5657,10 +5652,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628716</v>
+        <v>628595</v>
       </c>
       <c r="R51" t="n">
-        <v>6918568</v>
+        <v>6918652</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5693,6 +5688,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Möjligt att fler exemplar gömmer sig blåbärsriset/ mossan</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -2884,7 +2884,7 @@
         <v>127777664</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127776955</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28766-2025 artfynd.xlsx
+++ b/artfynd/A 28766-2025 artfynd.xlsx
@@ -2884,7 +2884,7 @@
         <v>127777664</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127776955</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
